--- a/environment/seed/sources/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
+++ b/environment/seed/sources/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="R1dc7ebfb6975451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="Rbeb63e427fba4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Authority" sheetId="3" r:id="Rdbe352a0de2c4ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="4" r:id="R424d3f37c0694fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="5" r:id="R04fb31a0f3ae4c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="6" r:id="R47de54231de348c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Execution" sheetId="7" r:id="R7f3143b92f064326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Rf4888aa5b5ab4623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="R90adb9c2d0964e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="R6176971d7bd54b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Authority" sheetId="3" r:id="R68d9e667df264edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="4" r:id="Rea1d39ada1cd4a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="5" r:id="Rb682917fa0e74c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="6" r:id="R6f700491523f4ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Execution" sheetId="7" r:id="R950509ee15ef4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R327d31c450c44878"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,8 +57,9 @@
       <x:name val="Aptos"/>
     </x:font>
     <x:font>
-      <x:sz val="9"/>
-      <x:color rgb="FF52655C"/>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2A4337"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -159,20 +160,20 @@
       <x:top style="thin">
         <x:color rgb="FFD8D0C6"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD8D0C6"/>
-      </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
         <x:color rgb="FFD8D0C6"/>
       </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8D0C6"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -238,18 +239,47 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -259,7 +289,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{88DF84C4-467D-4305-B76D-B191C84DBBD3}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{4F0CFD4D-9CDB-4176-9E2A-5A351BEAA3FF}"/>
 </xltc:personList>
 </file>
 
@@ -7447,19 +7477,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Revenue Burn</x:v>
+        <x:v>FY27 backlog burn | planning cases</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -7471,7 +7501,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
+        <x:v>Build from the controlled source schedules; keep probability plan, signed commitment, and pipeline distinct</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -7483,319 +7513,223 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Signed backlog</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>FY27 revenue</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>First constrained month</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Unresolved hours</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Remediation cost</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Release conclusion</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>signed_backlog</x:v>
+      <x:c r="A5" s="35" t="str">
+        <x:v>Approved probability plan</x:v>
       </x:c>
       <x:c r="B5" s="35"/>
+      <x:c r="C5" s="35"/>
+      <x:c r="D5" s="35"/>
+      <x:c r="E5" s="35"/>
+      <x:c r="F5" s="35"/>
+      <x:c r="G5" s="35"/>
+      <x:c r="H5" s="35"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>fy27_backlog_revenue_burn</x:v>
+      <x:c r="A6" s="36" t="str">
+        <x:v>Full signed commitment</x:v>
       </x:c>
       <x:c r="B6" s="36"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>2026_07_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>2026_08_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>2026_09_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="C6" s="36"/>
+      <x:c r="D6" s="36"/>
+      <x:c r="E6" s="36"/>
+      <x:c r="F6" s="36"/>
+      <x:c r="G6" s="36"/>
+      <x:c r="H6" s="36"/>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="15" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>Probability-plan revenue</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>Gross-commitment revenue</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>Revenue variance</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>Probability-plan hours</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="str">
+        <x:v>Gross-commitment hours</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="str">
+        <x:v>Source / version</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="str">
+        <x:v>Control</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>2026_10_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B10" s="45"/>
+      <x:c r="C10" s="45"/>
+      <x:c r="D10" s="45"/>
+      <x:c r="E10" s="45"/>
+      <x:c r="F10" s="45"/>
+      <x:c r="G10" s="45"/>
+      <x:c r="H10" s="45"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>2026_11_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>2026_12_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B12" s="36"/>
+      <x:c r="A12" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B12" s="46"/>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>2027_01_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B13" s="36"/>
+      <x:c r="A13" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B13" s="46"/>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>2027_02_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B14" s="36"/>
+      <x:c r="A14" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B14" s="46"/>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>2027_03_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B15" s="36"/>
+      <x:c r="A15" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B15" s="46"/>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>2027_04_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B16" s="36"/>
+      <x:c r="A16" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B16" s="46"/>
+      <x:c r="C16" s="46"/>
+      <x:c r="D16" s="46"/>
+      <x:c r="E16" s="46"/>
+      <x:c r="F16" s="46"/>
+      <x:c r="G16" s="46"/>
+      <x:c r="H16" s="46"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>2027_05_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B17" s="36"/>
+      <x:c r="A17" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B17" s="46"/>
+      <x:c r="C17" s="46"/>
+      <x:c r="D17" s="46"/>
+      <x:c r="E17" s="46"/>
+      <x:c r="F17" s="46"/>
+      <x:c r="G17" s="46"/>
+      <x:c r="H17" s="46"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>2027_06_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B18" s="36"/>
+      <x:c r="A18" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B18" s="46"/>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
+      <x:c r="G18" s="46"/>
+      <x:c r="H18" s="46"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>gross_commitment_2026_07_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B19" s="36"/>
+      <x:c r="A19" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B19" s="46"/>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
+      <x:c r="G19" s="46"/>
+      <x:c r="H19" s="46"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>gross_commitment_2026_08_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B20" s="36"/>
+      <x:c r="A20" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B20" s="46"/>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="46"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>gross_commitment_2026_09_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B21" s="36"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>gross_commitment_2026_10_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B22" s="36"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>gross_commitment_2026_11_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B23" s="36"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>gross_commitment_2026_12_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B24" s="36"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>gross_commitment_2027_01_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B25" s="36"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>gross_commitment_2027_02_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B26" s="36"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>gross_commitment_2027_03_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B27" s="36"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>gross_commitment_2027_04_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B28" s="36"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="33" t="str">
-        <x:v>gross_commitment_2027_05_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B29" s="36"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="33" t="str">
-        <x:v>gross_commitment_2027_06_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B30" s="36"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="34" t="str">
-        <x:v>gross_commitment_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B31" s="37"/>
-    </x:row>
-    <x:row r="34" ht="30" customHeight="1">
-      <x:c r="A34" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B34" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C34" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E34" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H34" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="40"/>
-      <x:c r="B35" s="40"/>
-      <x:c r="C35" s="40"/>
-      <x:c r="D35" s="40"/>
-      <x:c r="E35" s="40"/>
-      <x:c r="F35" s="40"/>
-      <x:c r="G35" s="40"/>
-      <x:c r="H35" s="40"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="41"/>
-      <x:c r="B36" s="41"/>
-      <x:c r="C36" s="41"/>
-      <x:c r="D36" s="41"/>
-      <x:c r="E36" s="41"/>
-      <x:c r="F36" s="41"/>
-      <x:c r="G36" s="41"/>
-      <x:c r="H36" s="41"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="41"/>
-      <x:c r="B37" s="41"/>
-      <x:c r="C37" s="41"/>
-      <x:c r="D37" s="41"/>
-      <x:c r="E37" s="41"/>
-      <x:c r="F37" s="41"/>
-      <x:c r="G37" s="41"/>
-      <x:c r="H37" s="41"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="41"/>
-      <x:c r="B38" s="41"/>
-      <x:c r="C38" s="41"/>
-      <x:c r="D38" s="41"/>
-      <x:c r="E38" s="41"/>
-      <x:c r="F38" s="41"/>
-      <x:c r="G38" s="41"/>
-      <x:c r="H38" s="41"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="41"/>
-      <x:c r="B39" s="41"/>
-      <x:c r="C39" s="41"/>
-      <x:c r="D39" s="41"/>
-      <x:c r="E39" s="41"/>
-      <x:c r="F39" s="41"/>
-      <x:c r="G39" s="41"/>
-      <x:c r="H39" s="41"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="41"/>
-      <x:c r="B40" s="41"/>
-      <x:c r="C40" s="41"/>
-      <x:c r="D40" s="41"/>
-      <x:c r="E40" s="41"/>
-      <x:c r="F40" s="41"/>
-      <x:c r="G40" s="41"/>
-      <x:c r="H40" s="41"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="41"/>
-      <x:c r="B41" s="41"/>
-      <x:c r="C41" s="41"/>
-      <x:c r="D41" s="41"/>
-      <x:c r="E41" s="41"/>
-      <x:c r="F41" s="41"/>
-      <x:c r="G41" s="41"/>
-      <x:c r="H41" s="41"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="41"/>
-      <x:c r="B42" s="41"/>
-      <x:c r="C42" s="41"/>
-      <x:c r="D42" s="41"/>
-      <x:c r="E42" s="41"/>
-      <x:c r="F42" s="41"/>
-      <x:c r="G42" s="41"/>
-      <x:c r="H42" s="41"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="41"/>
-      <x:c r="B43" s="41"/>
-      <x:c r="C43" s="41"/>
-      <x:c r="D43" s="41"/>
-      <x:c r="E43" s="41"/>
-      <x:c r="F43" s="41"/>
-      <x:c r="G43" s="41"/>
-      <x:c r="H43" s="41"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="41"/>
-      <x:c r="B44" s="41"/>
-      <x:c r="C44" s="41"/>
-      <x:c r="D44" s="41"/>
-      <x:c r="E44" s="41"/>
-      <x:c r="F44" s="41"/>
-      <x:c r="G44" s="41"/>
-      <x:c r="H44" s="41"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="41"/>
-      <x:c r="B45" s="41"/>
-      <x:c r="C45" s="41"/>
-      <x:c r="D45" s="41"/>
-      <x:c r="E45" s="41"/>
-      <x:c r="F45" s="41"/>
-      <x:c r="G45" s="41"/>
-      <x:c r="H45" s="41"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="42"/>
-      <x:c r="B46" s="42"/>
-      <x:c r="C46" s="42"/>
-      <x:c r="D46" s="42"/>
-      <x:c r="E46" s="42"/>
-      <x:c r="F46" s="42"/>
-      <x:c r="G46" s="42"/>
-      <x:c r="H46" s="42"/>
+      <x:c r="A21" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B21" s="47"/>
+      <x:c r="C21" s="47"/>
+      <x:c r="D21" s="47"/>
+      <x:c r="E21" s="47"/>
+      <x:c r="F21" s="47"/>
+      <x:c r="G21" s="47"/>
+      <x:c r="H21" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7810,19 +7744,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Labor Capacity</x:v>
+        <x:v>FY27 labor capacity | approved availability</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -7831,10 +7766,11 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
+        <x:v>Reconcile recurring capacity and keep ordinary availability separate from emergency response</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -7843,687 +7779,197 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Permitted overtime</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Planned subcontractable</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Base available hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Emergency OT capacity</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Contingent surge capacity</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Remediated available hours</x:v>
+      </x:c>
+      <x:c r="I4" s="17" t="str">
+        <x:v>Source / authority</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>fy27_required_hours</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B5" s="45"/>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>fy27_available_hours</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B6" s="46"/>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>2026_07_required_hours</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B7" s="46"/>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>2026_07_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B8" s="46"/>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>2026_07_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>2026_07_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B10" s="46"/>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>2026_07_available_hours</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>2026_07_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B12" s="36"/>
+      <x:c r="A12" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B12" s="46"/>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
+      <x:c r="I12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>2026_08_required_hours</x:v>
-      </x:c>
-      <x:c r="B13" s="36"/>
+      <x:c r="A13" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B13" s="46"/>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+      <x:c r="I13" s="46"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>2026_08_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B14" s="36"/>
+      <x:c r="A14" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B14" s="46"/>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+      <x:c r="I14" s="46"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>2026_08_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B15" s="36"/>
+      <x:c r="A15" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B15" s="46"/>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+      <x:c r="I15" s="46"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>2026_08_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B16" s="36"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>2026_08_available_hours</x:v>
-      </x:c>
-      <x:c r="B17" s="36"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>2026_08_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B18" s="36"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>2026_09_required_hours</x:v>
-      </x:c>
-      <x:c r="B19" s="36"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>2026_09_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B20" s="36"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>2026_09_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B21" s="36"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>2026_09_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B22" s="36"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>2026_09_available_hours</x:v>
-      </x:c>
-      <x:c r="B23" s="36"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>2026_09_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B24" s="36"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>2026_10_required_hours</x:v>
-      </x:c>
-      <x:c r="B25" s="36"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>2026_10_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B26" s="36"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>2026_10_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B27" s="36"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>2026_10_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B28" s="36"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="33" t="str">
-        <x:v>2026_10_available_hours</x:v>
-      </x:c>
-      <x:c r="B29" s="36"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="33" t="str">
-        <x:v>2026_10_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B30" s="36"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="33" t="str">
-        <x:v>2026_11_required_hours</x:v>
-      </x:c>
-      <x:c r="B31" s="36"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="33" t="str">
-        <x:v>2026_11_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B32" s="36"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="33" t="str">
-        <x:v>2026_11_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B33" s="36"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="33" t="str">
-        <x:v>2026_11_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B34" s="36"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="33" t="str">
-        <x:v>2026_11_available_hours</x:v>
-      </x:c>
-      <x:c r="B35" s="36"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="33" t="str">
-        <x:v>2026_11_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B36" s="36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="33" t="str">
-        <x:v>2026_12_required_hours</x:v>
-      </x:c>
-      <x:c r="B37" s="36"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="33" t="str">
-        <x:v>2026_12_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B38" s="36"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="33" t="str">
-        <x:v>2026_12_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B39" s="36"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="33" t="str">
-        <x:v>2026_12_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B40" s="36"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="33" t="str">
-        <x:v>2026_12_available_hours</x:v>
-      </x:c>
-      <x:c r="B41" s="36"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="33" t="str">
-        <x:v>2026_12_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B42" s="36"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="33" t="str">
-        <x:v>2027_01_required_hours</x:v>
-      </x:c>
-      <x:c r="B43" s="36"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="33" t="str">
-        <x:v>2027_01_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B44" s="36"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="33" t="str">
-        <x:v>2027_01_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B45" s="36"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="33" t="str">
-        <x:v>2027_01_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B46" s="36"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="33" t="str">
-        <x:v>2027_01_available_hours</x:v>
-      </x:c>
-      <x:c r="B47" s="36"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="33" t="str">
-        <x:v>2027_01_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B48" s="36"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="33" t="str">
-        <x:v>2027_02_required_hours</x:v>
-      </x:c>
-      <x:c r="B49" s="36"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="33" t="str">
-        <x:v>2027_02_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B50" s="36"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="33" t="str">
-        <x:v>2027_02_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B51" s="36"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="33" t="str">
-        <x:v>2027_02_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B52" s="36"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="33" t="str">
-        <x:v>2027_02_available_hours</x:v>
-      </x:c>
-      <x:c r="B53" s="36"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="33" t="str">
-        <x:v>2027_02_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B54" s="36"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="33" t="str">
-        <x:v>2027_03_required_hours</x:v>
-      </x:c>
-      <x:c r="B55" s="36"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="33" t="str">
-        <x:v>2027_03_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B56" s="36"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="33" t="str">
-        <x:v>2027_03_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B57" s="36"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="33" t="str">
-        <x:v>2027_03_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B58" s="36"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="33" t="str">
-        <x:v>2027_03_available_hours</x:v>
-      </x:c>
-      <x:c r="B59" s="36"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="33" t="str">
-        <x:v>2027_03_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B60" s="36"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="33" t="str">
-        <x:v>2027_04_required_hours</x:v>
-      </x:c>
-      <x:c r="B61" s="36"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="33" t="str">
-        <x:v>2027_04_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B62" s="36"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="33" t="str">
-        <x:v>2027_04_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B63" s="36"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="33" t="str">
-        <x:v>2027_04_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B64" s="36"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="33" t="str">
-        <x:v>2027_04_available_hours</x:v>
-      </x:c>
-      <x:c r="B65" s="36"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="33" t="str">
-        <x:v>2027_04_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B66" s="36"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="33" t="str">
-        <x:v>2027_05_required_hours</x:v>
-      </x:c>
-      <x:c r="B67" s="36"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="33" t="str">
-        <x:v>2027_05_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B68" s="36"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="33" t="str">
-        <x:v>2027_05_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B69" s="36"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="33" t="str">
-        <x:v>2027_05_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B70" s="36"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="33" t="str">
-        <x:v>2027_05_available_hours</x:v>
-      </x:c>
-      <x:c r="B71" s="36"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="33" t="str">
-        <x:v>2027_05_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B72" s="36"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="33" t="str">
-        <x:v>2027_06_required_hours</x:v>
-      </x:c>
-      <x:c r="B73" s="36"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="33" t="str">
-        <x:v>2027_06_productive_internal_hours</x:v>
-      </x:c>
-      <x:c r="B74" s="36"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="33" t="str">
-        <x:v>2027_06_permitted_overtime_hours</x:v>
-      </x:c>
-      <x:c r="B75" s="36"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="33" t="str">
-        <x:v>2027_06_subcontractable_hours</x:v>
-      </x:c>
-      <x:c r="B76" s="36"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="33" t="str">
-        <x:v>2027_06_available_hours</x:v>
-      </x:c>
-      <x:c r="B77" s="36"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="33" t="str">
-        <x:v>2027_06_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B78" s="36"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="33" t="str">
-        <x:v>gross_commitment_2026_07_required_hours</x:v>
-      </x:c>
-      <x:c r="B79" s="36"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="33" t="str">
-        <x:v>gross_commitment_2026_08_required_hours</x:v>
-      </x:c>
-      <x:c r="B80" s="36"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="33" t="str">
-        <x:v>gross_commitment_2026_09_required_hours</x:v>
-      </x:c>
-      <x:c r="B81" s="36"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="33" t="str">
-        <x:v>gross_commitment_2026_10_required_hours</x:v>
-      </x:c>
-      <x:c r="B82" s="36"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="33" t="str">
-        <x:v>gross_commitment_2026_11_required_hours</x:v>
-      </x:c>
-      <x:c r="B83" s="36"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="33" t="str">
-        <x:v>gross_commitment_2026_12_required_hours</x:v>
-      </x:c>
-      <x:c r="B84" s="36"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="33" t="str">
-        <x:v>gross_commitment_2027_01_required_hours</x:v>
-      </x:c>
-      <x:c r="B85" s="36"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="33" t="str">
-        <x:v>gross_commitment_2027_02_required_hours</x:v>
-      </x:c>
-      <x:c r="B86" s="36"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="33" t="str">
-        <x:v>gross_commitment_2027_03_required_hours</x:v>
-      </x:c>
-      <x:c r="B87" s="36"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="33" t="str">
-        <x:v>gross_commitment_2027_04_required_hours</x:v>
-      </x:c>
-      <x:c r="B88" s="36"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="33" t="str">
-        <x:v>gross_commitment_2027_05_required_hours</x:v>
-      </x:c>
-      <x:c r="B89" s="36"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="33" t="str">
-        <x:v>gross_commitment_2027_06_required_hours</x:v>
-      </x:c>
-      <x:c r="B90" s="36"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="34" t="str">
-        <x:v>gross_commitment_required_hours</x:v>
-      </x:c>
-      <x:c r="B91" s="37"/>
-    </x:row>
-    <x:row r="94" ht="30" customHeight="1">
-      <x:c r="A94" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B94" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C94" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D94" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E94" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F94" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G94" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H94" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="40"/>
-      <x:c r="B95" s="40"/>
-      <x:c r="C95" s="40"/>
-      <x:c r="D95" s="40"/>
-      <x:c r="E95" s="40"/>
-      <x:c r="F95" s="40"/>
-      <x:c r="G95" s="40"/>
-      <x:c r="H95" s="40"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="41"/>
-      <x:c r="B96" s="41"/>
-      <x:c r="C96" s="41"/>
-      <x:c r="D96" s="41"/>
-      <x:c r="E96" s="41"/>
-      <x:c r="F96" s="41"/>
-      <x:c r="G96" s="41"/>
-      <x:c r="H96" s="41"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="41"/>
-      <x:c r="B97" s="41"/>
-      <x:c r="C97" s="41"/>
-      <x:c r="D97" s="41"/>
-      <x:c r="E97" s="41"/>
-      <x:c r="F97" s="41"/>
-      <x:c r="G97" s="41"/>
-      <x:c r="H97" s="41"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="41"/>
-      <x:c r="B98" s="41"/>
-      <x:c r="C98" s="41"/>
-      <x:c r="D98" s="41"/>
-      <x:c r="E98" s="41"/>
-      <x:c r="F98" s="41"/>
-      <x:c r="G98" s="41"/>
-      <x:c r="H98" s="41"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="41"/>
-      <x:c r="B99" s="41"/>
-      <x:c r="C99" s="41"/>
-      <x:c r="D99" s="41"/>
-      <x:c r="E99" s="41"/>
-      <x:c r="F99" s="41"/>
-      <x:c r="G99" s="41"/>
-      <x:c r="H99" s="41"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="41"/>
-      <x:c r="B100" s="41"/>
-      <x:c r="C100" s="41"/>
-      <x:c r="D100" s="41"/>
-      <x:c r="E100" s="41"/>
-      <x:c r="F100" s="41"/>
-      <x:c r="G100" s="41"/>
-      <x:c r="H100" s="41"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="41"/>
-      <x:c r="B101" s="41"/>
-      <x:c r="C101" s="41"/>
-      <x:c r="D101" s="41"/>
-      <x:c r="E101" s="41"/>
-      <x:c r="F101" s="41"/>
-      <x:c r="G101" s="41"/>
-      <x:c r="H101" s="41"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="41"/>
-      <x:c r="B102" s="41"/>
-      <x:c r="C102" s="41"/>
-      <x:c r="D102" s="41"/>
-      <x:c r="E102" s="41"/>
-      <x:c r="F102" s="41"/>
-      <x:c r="G102" s="41"/>
-      <x:c r="H102" s="41"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="41"/>
-      <x:c r="B103" s="41"/>
-      <x:c r="C103" s="41"/>
-      <x:c r="D103" s="41"/>
-      <x:c r="E103" s="41"/>
-      <x:c r="F103" s="41"/>
-      <x:c r="G103" s="41"/>
-      <x:c r="H103" s="41"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="41"/>
-      <x:c r="B104" s="41"/>
-      <x:c r="C104" s="41"/>
-      <x:c r="D104" s="41"/>
-      <x:c r="E104" s="41"/>
-      <x:c r="F104" s="41"/>
-      <x:c r="G104" s="41"/>
-      <x:c r="H104" s="41"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="41"/>
-      <x:c r="B105" s="41"/>
-      <x:c r="C105" s="41"/>
-      <x:c r="D105" s="41"/>
-      <x:c r="E105" s="41"/>
-      <x:c r="F105" s="41"/>
-      <x:c r="G105" s="41"/>
-      <x:c r="H105" s="41"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="42"/>
-      <x:c r="B106" s="42"/>
-      <x:c r="C106" s="42"/>
-      <x:c r="D106" s="42"/>
-      <x:c r="E106" s="42"/>
-      <x:c r="F106" s="42"/>
-      <x:c r="G106" s="42"/>
-      <x:c r="H106" s="42"/>
+      <x:c r="A16" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B16" s="47"/>
+      <x:c r="C16" s="47"/>
+      <x:c r="D16" s="47"/>
+      <x:c r="E16" s="47"/>
+      <x:c r="F16" s="47"/>
+      <x:c r="G16" s="47"/>
+      <x:c r="H16" s="47"/>
+      <x:c r="I16" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8533,19 +7979,22 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Gap Analysis</x:v>
+        <x:v>FY27 capacity response | case comparison</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -8554,10 +8003,13 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
+        <x:v>Capacity gap = required hours less available hours; positive is a shortfall and negative is spare capacity</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -8566,1479 +8018,457 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Available hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Capacity gap</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Emergency OT used</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Surge used</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>Unresolved shortfall</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Remediation cost</x:v>
+      </x:c>
+      <x:c r="K4" s="17" t="str">
+        <x:v>Decision</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>constrained_month_count</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="45" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B5" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
+      <x:c r="J5" s="45"/>
+      <x:c r="K5" s="45"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>first_constrained_month</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B6" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
+      <x:c r="J6" s="46"/>
+      <x:c r="K6" s="46"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>maximum_capacity_shortfall_hours</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B7" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
+      <x:c r="J7" s="46"/>
+      <x:c r="K7" s="46"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>2026_07_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B8" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
+      <x:c r="J8" s="46"/>
+      <x:c r="K8" s="46"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>2026_07_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B9" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+      <x:c r="J9" s="46"/>
+      <x:c r="K9" s="46"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>2026_07_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B10" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
+      <x:c r="J10" s="46"/>
+      <x:c r="K10" s="46"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>2026_07_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B11" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
+      <x:c r="J11" s="46"/>
+      <x:c r="K11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>2026_07_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B12" s="36"/>
+      <x:c r="A12" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B12" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
+      <x:c r="I12" s="46"/>
+      <x:c r="J12" s="46"/>
+      <x:c r="K12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>2026_07_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B13" s="36"/>
+      <x:c r="A13" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B13" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+      <x:c r="I13" s="46"/>
+      <x:c r="J13" s="46"/>
+      <x:c r="K13" s="46"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>2026_07_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B14" s="36"/>
+      <x:c r="A14" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B14" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+      <x:c r="I14" s="46"/>
+      <x:c r="J14" s="46"/>
+      <x:c r="K14" s="46"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>2026_07_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B15" s="36"/>
+      <x:c r="A15" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B15" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+      <x:c r="I15" s="46"/>
+      <x:c r="J15" s="46"/>
+      <x:c r="K15" s="46"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>2026_07_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B16" s="36"/>
+      <x:c r="A16" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B16" s="46" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="C16" s="46"/>
+      <x:c r="D16" s="46"/>
+      <x:c r="E16" s="46"/>
+      <x:c r="F16" s="46"/>
+      <x:c r="G16" s="46"/>
+      <x:c r="H16" s="46"/>
+      <x:c r="I16" s="46"/>
+      <x:c r="J16" s="46"/>
+      <x:c r="K16" s="46"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>2026_07_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B17" s="36"/>
+      <x:c r="A17" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B17" s="46" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="C17" s="46"/>
+      <x:c r="D17" s="46"/>
+      <x:c r="E17" s="46"/>
+      <x:c r="F17" s="46"/>
+      <x:c r="G17" s="46"/>
+      <x:c r="H17" s="46"/>
+      <x:c r="I17" s="46"/>
+      <x:c r="J17" s="46"/>
+      <x:c r="K17" s="46"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>2026_07_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B18" s="36"/>
+      <x:c r="A18" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B18" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
+      <x:c r="G18" s="46"/>
+      <x:c r="H18" s="46"/>
+      <x:c r="I18" s="46"/>
+      <x:c r="J18" s="46"/>
+      <x:c r="K18" s="46"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>2026_08_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B19" s="36"/>
+      <x:c r="A19" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B19" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
+      <x:c r="G19" s="46"/>
+      <x:c r="H19" s="46"/>
+      <x:c r="I19" s="46"/>
+      <x:c r="J19" s="46"/>
+      <x:c r="K19" s="46"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>2026_08_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B20" s="36"/>
+      <x:c r="A20" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B20" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="46"/>
+      <x:c r="I20" s="46"/>
+      <x:c r="J20" s="46"/>
+      <x:c r="K20" s="46"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>2026_08_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B21" s="36"/>
+      <x:c r="A21" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B21" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="46"/>
+      <x:c r="G21" s="46"/>
+      <x:c r="H21" s="46"/>
+      <x:c r="I21" s="46"/>
+      <x:c r="J21" s="46"/>
+      <x:c r="K21" s="46"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>2026_08_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B22" s="36"/>
+      <x:c r="A22" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B22" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="46"/>
+      <x:c r="G22" s="46"/>
+      <x:c r="H22" s="46"/>
+      <x:c r="I22" s="46"/>
+      <x:c r="J22" s="46"/>
+      <x:c r="K22" s="46"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>2026_08_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B23" s="36"/>
+      <x:c r="A23" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B23" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="46"/>
+      <x:c r="G23" s="46"/>
+      <x:c r="H23" s="46"/>
+      <x:c r="I23" s="46"/>
+      <x:c r="J23" s="46"/>
+      <x:c r="K23" s="46"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>2026_08_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B24" s="36"/>
+      <x:c r="A24" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B24" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="46"/>
+      <x:c r="G24" s="46"/>
+      <x:c r="H24" s="46"/>
+      <x:c r="I24" s="46"/>
+      <x:c r="J24" s="46"/>
+      <x:c r="K24" s="46"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>2026_08_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B25" s="36"/>
+      <x:c r="A25" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B25" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
+      <x:c r="G25" s="46"/>
+      <x:c r="H25" s="46"/>
+      <x:c r="I25" s="46"/>
+      <x:c r="J25" s="46"/>
+      <x:c r="K25" s="46"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>2026_08_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B26" s="36"/>
+      <x:c r="A26" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B26" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="C26" s="46"/>
+      <x:c r="D26" s="46"/>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="46"/>
+      <x:c r="G26" s="46"/>
+      <x:c r="H26" s="46"/>
+      <x:c r="I26" s="46"/>
+      <x:c r="J26" s="46"/>
+      <x:c r="K26" s="46"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>2026_08_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B27" s="36"/>
+      <x:c r="A27" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B27" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="46"/>
+      <x:c r="G27" s="46"/>
+      <x:c r="H27" s="46"/>
+      <x:c r="I27" s="46"/>
+      <x:c r="J27" s="46"/>
+      <x:c r="K27" s="46"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>2026_08_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B28" s="36"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="33" t="str">
-        <x:v>2026_08_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B29" s="36"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="33" t="str">
-        <x:v>2026_09_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B30" s="36"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="33" t="str">
-        <x:v>2026_09_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B31" s="36"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="33" t="str">
-        <x:v>2026_09_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B32" s="36"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="33" t="str">
-        <x:v>2026_09_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B33" s="36"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="33" t="str">
-        <x:v>2026_09_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B34" s="36"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="33" t="str">
-        <x:v>2026_09_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B35" s="36"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="33" t="str">
-        <x:v>2026_09_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B36" s="36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="33" t="str">
-        <x:v>2026_09_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B37" s="36"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="33" t="str">
-        <x:v>2026_09_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B38" s="36"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="33" t="str">
-        <x:v>2026_09_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B39" s="36"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="33" t="str">
-        <x:v>2026_09_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B40" s="36"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="33" t="str">
-        <x:v>2026_10_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B41" s="36"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="33" t="str">
-        <x:v>2026_10_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B42" s="36"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="33" t="str">
-        <x:v>2026_10_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B43" s="36"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="33" t="str">
-        <x:v>2026_10_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B44" s="36"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="33" t="str">
-        <x:v>2026_10_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B45" s="36"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="33" t="str">
-        <x:v>2026_10_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B46" s="36"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="33" t="str">
-        <x:v>2026_10_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B47" s="36"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="33" t="str">
-        <x:v>2026_10_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B48" s="36"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="33" t="str">
-        <x:v>2026_10_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B49" s="36"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="33" t="str">
-        <x:v>2026_10_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B50" s="36"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="33" t="str">
-        <x:v>2026_10_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B51" s="36"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="33" t="str">
-        <x:v>2026_11_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B52" s="36"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="33" t="str">
-        <x:v>2026_11_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B53" s="36"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="33" t="str">
-        <x:v>2026_11_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B54" s="36"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="33" t="str">
-        <x:v>2026_11_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B55" s="36"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="33" t="str">
-        <x:v>2026_11_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B56" s="36"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="33" t="str">
-        <x:v>2026_11_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B57" s="36"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="33" t="str">
-        <x:v>2026_11_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B58" s="36"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="33" t="str">
-        <x:v>2026_11_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B59" s="36"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="33" t="str">
-        <x:v>2026_11_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B60" s="36"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="33" t="str">
-        <x:v>2026_11_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B61" s="36"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="33" t="str">
-        <x:v>2026_11_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B62" s="36"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="33" t="str">
-        <x:v>2026_12_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B63" s="36"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="33" t="str">
-        <x:v>2026_12_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B64" s="36"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="33" t="str">
-        <x:v>2026_12_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B65" s="36"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="33" t="str">
-        <x:v>2026_12_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B66" s="36"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="33" t="str">
-        <x:v>2026_12_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B67" s="36"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="33" t="str">
-        <x:v>2026_12_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B68" s="36"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="33" t="str">
-        <x:v>2026_12_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B69" s="36"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="33" t="str">
-        <x:v>2026_12_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B70" s="36"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="33" t="str">
-        <x:v>2026_12_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B71" s="36"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="33" t="str">
-        <x:v>2026_12_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B72" s="36"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="33" t="str">
-        <x:v>2026_12_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B73" s="36"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="33" t="str">
-        <x:v>2027_01_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B74" s="36"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="33" t="str">
-        <x:v>2027_01_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B75" s="36"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="33" t="str">
-        <x:v>2027_01_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B76" s="36"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="33" t="str">
-        <x:v>2027_01_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B77" s="36"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="33" t="str">
-        <x:v>2027_01_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B78" s="36"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="33" t="str">
-        <x:v>2027_01_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B79" s="36"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="33" t="str">
-        <x:v>2027_01_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B80" s="36"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="33" t="str">
-        <x:v>2027_01_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B81" s="36"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="33" t="str">
-        <x:v>2027_01_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B82" s="36"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="33" t="str">
-        <x:v>2027_01_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B83" s="36"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="33" t="str">
-        <x:v>2027_01_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B84" s="36"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="33" t="str">
-        <x:v>2027_02_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B85" s="36"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="33" t="str">
-        <x:v>2027_02_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B86" s="36"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="33" t="str">
-        <x:v>2027_02_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B87" s="36"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="33" t="str">
-        <x:v>2027_02_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B88" s="36"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="33" t="str">
-        <x:v>2027_02_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B89" s="36"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="33" t="str">
-        <x:v>2027_02_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B90" s="36"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="33" t="str">
-        <x:v>2027_02_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B91" s="36"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92" s="33" t="str">
-        <x:v>2027_02_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B92" s="36"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93" s="33" t="str">
-        <x:v>2027_02_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B93" s="36"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="33" t="str">
-        <x:v>2027_02_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B94" s="36"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="33" t="str">
-        <x:v>2027_02_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B95" s="36"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="33" t="str">
-        <x:v>2027_03_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B96" s="36"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="33" t="str">
-        <x:v>2027_03_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B97" s="36"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="33" t="str">
-        <x:v>2027_03_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B98" s="36"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="33" t="str">
-        <x:v>2027_03_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B99" s="36"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="33" t="str">
-        <x:v>2027_03_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B100" s="36"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="33" t="str">
-        <x:v>2027_03_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B101" s="36"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="33" t="str">
-        <x:v>2027_03_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B102" s="36"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="33" t="str">
-        <x:v>2027_03_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B103" s="36"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="33" t="str">
-        <x:v>2027_03_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B104" s="36"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="33" t="str">
-        <x:v>2027_03_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B105" s="36"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="33" t="str">
-        <x:v>2027_03_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B106" s="36"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="33" t="str">
-        <x:v>2027_04_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B107" s="36"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="33" t="str">
-        <x:v>2027_04_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B108" s="36"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="A109" s="33" t="str">
-        <x:v>2027_04_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B109" s="36"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="33" t="str">
-        <x:v>2027_04_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B110" s="36"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="33" t="str">
-        <x:v>2027_04_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B111" s="36"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="A112" s="33" t="str">
-        <x:v>2027_04_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B112" s="36"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="A113" s="33" t="str">
-        <x:v>2027_04_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B113" s="36"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="33" t="str">
-        <x:v>2027_04_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B114" s="36"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="33" t="str">
-        <x:v>2027_04_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B115" s="36"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="33" t="str">
-        <x:v>2027_04_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B116" s="36"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="33" t="str">
-        <x:v>2027_04_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B117" s="36"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="33" t="str">
-        <x:v>2027_05_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B118" s="36"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="A119" s="33" t="str">
-        <x:v>2027_05_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B119" s="36"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="A120" s="33" t="str">
-        <x:v>2027_05_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B120" s="36"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="A121" s="33" t="str">
-        <x:v>2027_05_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B121" s="36"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="A122" s="33" t="str">
-        <x:v>2027_05_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B122" s="36"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="A123" s="33" t="str">
-        <x:v>2027_05_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B123" s="36"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="A124" s="33" t="str">
-        <x:v>2027_05_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B124" s="36"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="A125" s="33" t="str">
-        <x:v>2027_05_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B125" s="36"/>
-    </x:row>
-    <x:row r="126">
-      <x:c r="A126" s="33" t="str">
-        <x:v>2027_05_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B126" s="36"/>
-    </x:row>
-    <x:row r="127">
-      <x:c r="A127" s="33" t="str">
-        <x:v>2027_05_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B127" s="36"/>
-    </x:row>
-    <x:row r="128">
-      <x:c r="A128" s="33" t="str">
-        <x:v>2027_05_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B128" s="36"/>
-    </x:row>
-    <x:row r="129">
-      <x:c r="A129" s="33" t="str">
-        <x:v>2027_06_capacity_gap_hours</x:v>
-      </x:c>
-      <x:c r="B129" s="36"/>
-    </x:row>
-    <x:row r="130">
-      <x:c r="A130" s="33" t="str">
-        <x:v>2027_06_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B130" s="36"/>
-    </x:row>
-    <x:row r="131">
-      <x:c r="A131" s="33" t="str">
-        <x:v>2027_06_emergency_overtime_capacity</x:v>
-      </x:c>
-      <x:c r="B131" s="36"/>
-    </x:row>
-    <x:row r="132">
-      <x:c r="A132" s="33" t="str">
-        <x:v>2027_06_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B132" s="36"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="A133" s="33" t="str">
-        <x:v>2027_06_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B133" s="36"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="33" t="str">
-        <x:v>2027_06_contingent_subcontract_capacity</x:v>
-      </x:c>
-      <x:c r="B134" s="36"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="33" t="str">
-        <x:v>2027_06_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B135" s="36"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="33" t="str">
-        <x:v>2027_06_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B136" s="36"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="33" t="str">
-        <x:v>2027_06_remediated_available_hours</x:v>
-      </x:c>
-      <x:c r="B137" s="36"/>
-    </x:row>
-    <x:row r="138">
-      <x:c r="A138" s="33" t="str">
-        <x:v>2027_06_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B138" s="36"/>
-    </x:row>
-    <x:row r="139">
-      <x:c r="A139" s="33" t="str">
-        <x:v>2027_06_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B139" s="36"/>
-    </x:row>
-    <x:row r="140">
-      <x:c r="A140" s="33" t="str">
-        <x:v>gross_commitment_2026_07_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B140" s="36"/>
-    </x:row>
-    <x:row r="141">
-      <x:c r="A141" s="33" t="str">
-        <x:v>gross_commitment_2026_07_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B141" s="36"/>
-    </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="33" t="str">
-        <x:v>gross_commitment_2026_07_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B142" s="36"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="33" t="str">
-        <x:v>gross_commitment_2026_07_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B143" s="36"/>
-    </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="33" t="str">
-        <x:v>gross_commitment_2026_07_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B144" s="36"/>
-    </x:row>
-    <x:row r="145">
-      <x:c r="A145" s="33" t="str">
-        <x:v>gross_commitment_2026_07_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B145" s="36"/>
-    </x:row>
-    <x:row r="146">
-      <x:c r="A146" s="33" t="str">
-        <x:v>gross_commitment_2026_07_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B146" s="36"/>
-    </x:row>
-    <x:row r="147">
-      <x:c r="A147" s="33" t="str">
-        <x:v>gross_commitment_2026_08_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B147" s="36"/>
-    </x:row>
-    <x:row r="148">
-      <x:c r="A148" s="33" t="str">
-        <x:v>gross_commitment_2026_08_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B148" s="36"/>
-    </x:row>
-    <x:row r="149">
-      <x:c r="A149" s="33" t="str">
-        <x:v>gross_commitment_2026_08_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B149" s="36"/>
-    </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="33" t="str">
-        <x:v>gross_commitment_2026_08_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B150" s="36"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="33" t="str">
-        <x:v>gross_commitment_2026_08_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B151" s="36"/>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="33" t="str">
-        <x:v>gross_commitment_2026_08_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B152" s="36"/>
-    </x:row>
-    <x:row r="153">
-      <x:c r="A153" s="33" t="str">
-        <x:v>gross_commitment_2026_08_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B153" s="36"/>
-    </x:row>
-    <x:row r="154">
-      <x:c r="A154" s="33" t="str">
-        <x:v>gross_commitment_2026_09_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B154" s="36"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
-        <x:v>gross_commitment_2026_09_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B155" s="36"/>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156" s="33" t="str">
-        <x:v>gross_commitment_2026_09_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B156" s="36"/>
-    </x:row>
-    <x:row r="157">
-      <x:c r="A157" s="33" t="str">
-        <x:v>gross_commitment_2026_09_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B157" s="36"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="33" t="str">
-        <x:v>gross_commitment_2026_09_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B158" s="36"/>
-    </x:row>
-    <x:row r="159">
-      <x:c r="A159" s="33" t="str">
-        <x:v>gross_commitment_2026_09_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B159" s="36"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="33" t="str">
-        <x:v>gross_commitment_2026_09_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B160" s="36"/>
-    </x:row>
-    <x:row r="161">
-      <x:c r="A161" s="33" t="str">
-        <x:v>gross_commitment_2026_10_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B161" s="36"/>
-    </x:row>
-    <x:row r="162">
-      <x:c r="A162" s="33" t="str">
-        <x:v>gross_commitment_2026_10_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B162" s="36"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" s="33" t="str">
-        <x:v>gross_commitment_2026_10_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B163" s="36"/>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164" s="33" t="str">
-        <x:v>gross_commitment_2026_10_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B164" s="36"/>
-    </x:row>
-    <x:row r="165">
-      <x:c r="A165" s="33" t="str">
-        <x:v>gross_commitment_2026_10_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B165" s="36"/>
-    </x:row>
-    <x:row r="166">
-      <x:c r="A166" s="33" t="str">
-        <x:v>gross_commitment_2026_10_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B166" s="36"/>
-    </x:row>
-    <x:row r="167">
-      <x:c r="A167" s="33" t="str">
-        <x:v>gross_commitment_2026_10_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B167" s="36"/>
-    </x:row>
-    <x:row r="168">
-      <x:c r="A168" s="33" t="str">
-        <x:v>gross_commitment_2026_11_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B168" s="36"/>
-    </x:row>
-    <x:row r="169">
-      <x:c r="A169" s="33" t="str">
-        <x:v>gross_commitment_2026_11_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B169" s="36"/>
-    </x:row>
-    <x:row r="170">
-      <x:c r="A170" s="33" t="str">
-        <x:v>gross_commitment_2026_11_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B170" s="36"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171" s="33" t="str">
-        <x:v>gross_commitment_2026_11_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B171" s="36"/>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172" s="33" t="str">
-        <x:v>gross_commitment_2026_11_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B172" s="36"/>
-    </x:row>
-    <x:row r="173">
-      <x:c r="A173" s="33" t="str">
-        <x:v>gross_commitment_2026_11_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B173" s="36"/>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174" s="33" t="str">
-        <x:v>gross_commitment_2026_11_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B174" s="36"/>
-    </x:row>
-    <x:row r="175">
-      <x:c r="A175" s="33" t="str">
-        <x:v>gross_commitment_2026_12_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B175" s="36"/>
-    </x:row>
-    <x:row r="176">
-      <x:c r="A176" s="33" t="str">
-        <x:v>gross_commitment_2026_12_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B176" s="36"/>
-    </x:row>
-    <x:row r="177">
-      <x:c r="A177" s="33" t="str">
-        <x:v>gross_commitment_2026_12_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B177" s="36"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178" s="33" t="str">
-        <x:v>gross_commitment_2026_12_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B178" s="36"/>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179" s="33" t="str">
-        <x:v>gross_commitment_2026_12_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B179" s="36"/>
-    </x:row>
-    <x:row r="180">
-      <x:c r="A180" s="33" t="str">
-        <x:v>gross_commitment_2026_12_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B180" s="36"/>
-    </x:row>
-    <x:row r="181">
-      <x:c r="A181" s="33" t="str">
-        <x:v>gross_commitment_2026_12_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B181" s="36"/>
-    </x:row>
-    <x:row r="182">
-      <x:c r="A182" s="33" t="str">
-        <x:v>gross_commitment_2027_01_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B182" s="36"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="33" t="str">
-        <x:v>gross_commitment_2027_01_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B183" s="36"/>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="33" t="str">
-        <x:v>gross_commitment_2027_01_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B184" s="36"/>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185" s="33" t="str">
-        <x:v>gross_commitment_2027_01_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B185" s="36"/>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186" s="33" t="str">
-        <x:v>gross_commitment_2027_01_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B186" s="36"/>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187" s="33" t="str">
-        <x:v>gross_commitment_2027_01_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B187" s="36"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" s="33" t="str">
-        <x:v>gross_commitment_2027_01_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B188" s="36"/>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" s="33" t="str">
-        <x:v>gross_commitment_2027_02_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B189" s="36"/>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190" s="33" t="str">
-        <x:v>gross_commitment_2027_02_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B190" s="36"/>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191" s="33" t="str">
-        <x:v>gross_commitment_2027_02_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B191" s="36"/>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192" s="33" t="str">
-        <x:v>gross_commitment_2027_02_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B192" s="36"/>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193" s="33" t="str">
-        <x:v>gross_commitment_2027_02_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B193" s="36"/>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194" s="33" t="str">
-        <x:v>gross_commitment_2027_02_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B194" s="36"/>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195" s="33" t="str">
-        <x:v>gross_commitment_2027_02_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B195" s="36"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" s="33" t="str">
-        <x:v>gross_commitment_2027_03_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B196" s="36"/>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" s="33" t="str">
-        <x:v>gross_commitment_2027_03_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B197" s="36"/>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198" s="33" t="str">
-        <x:v>gross_commitment_2027_03_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B198" s="36"/>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" s="33" t="str">
-        <x:v>gross_commitment_2027_03_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B199" s="36"/>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200" s="33" t="str">
-        <x:v>gross_commitment_2027_03_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B200" s="36"/>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201" s="33" t="str">
-        <x:v>gross_commitment_2027_03_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B201" s="36"/>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202" s="33" t="str">
-        <x:v>gross_commitment_2027_03_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B202" s="36"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203" s="33" t="str">
-        <x:v>gross_commitment_2027_04_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B203" s="36"/>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204" s="33" t="str">
-        <x:v>gross_commitment_2027_04_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B204" s="36"/>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A205" s="33" t="str">
-        <x:v>gross_commitment_2027_04_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B205" s="36"/>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A206" s="33" t="str">
-        <x:v>gross_commitment_2027_04_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B206" s="36"/>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A207" s="33" t="str">
-        <x:v>gross_commitment_2027_04_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B207" s="36"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208" s="33" t="str">
-        <x:v>gross_commitment_2027_04_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B208" s="36"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="33" t="str">
-        <x:v>gross_commitment_2027_04_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B209" s="36"/>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A210" s="33" t="str">
-        <x:v>gross_commitment_2027_05_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B210" s="36"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="33" t="str">
-        <x:v>gross_commitment_2027_05_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B211" s="36"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" s="33" t="str">
-        <x:v>gross_commitment_2027_05_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B212" s="36"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" s="33" t="str">
-        <x:v>gross_commitment_2027_05_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B213" s="36"/>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" s="33" t="str">
-        <x:v>gross_commitment_2027_05_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B214" s="36"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A215" s="33" t="str">
-        <x:v>gross_commitment_2027_05_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B215" s="36"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A216" s="33" t="str">
-        <x:v>gross_commitment_2027_05_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B216" s="36"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A217" s="33" t="str">
-        <x:v>gross_commitment_2027_06_base_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B217" s="36"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="A218" s="33" t="str">
-        <x:v>gross_commitment_2027_06_emergency_overtime_deployed</x:v>
-      </x:c>
-      <x:c r="B218" s="36"/>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A219" s="33" t="str">
-        <x:v>gross_commitment_2027_06_shortfall_after_emergency_overtime</x:v>
-      </x:c>
-      <x:c r="B219" s="36"/>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A220" s="33" t="str">
-        <x:v>gross_commitment_2027_06_contingent_subcontract_deployed</x:v>
-      </x:c>
-      <x:c r="B220" s="36"/>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="33" t="str">
-        <x:v>gross_commitment_2027_06_unresolved_capacity_shortfall</x:v>
-      </x:c>
-      <x:c r="B221" s="36"/>
-    </x:row>
-    <x:row r="222">
-      <x:c r="A222" s="33" t="str">
-        <x:v>gross_commitment_2027_06_incremental_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B222" s="36"/>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A223" s="34" t="str">
-        <x:v>gross_commitment_2027_06_capacity_release_status</x:v>
-      </x:c>
-      <x:c r="B223" s="37"/>
-    </x:row>
-    <x:row r="226" ht="30" customHeight="1">
-      <x:c r="A226" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B226" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C226" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D226" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E226" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F226" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G226" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H226" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227">
-      <x:c r="A227" s="40"/>
-      <x:c r="B227" s="40"/>
-      <x:c r="C227" s="40"/>
-      <x:c r="D227" s="40"/>
-      <x:c r="E227" s="40"/>
-      <x:c r="F227" s="40"/>
-      <x:c r="G227" s="40"/>
-      <x:c r="H227" s="40"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A228" s="41"/>
-      <x:c r="B228" s="41"/>
-      <x:c r="C228" s="41"/>
-      <x:c r="D228" s="41"/>
-      <x:c r="E228" s="41"/>
-      <x:c r="F228" s="41"/>
-      <x:c r="G228" s="41"/>
-      <x:c r="H228" s="41"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229" s="41"/>
-      <x:c r="B229" s="41"/>
-      <x:c r="C229" s="41"/>
-      <x:c r="D229" s="41"/>
-      <x:c r="E229" s="41"/>
-      <x:c r="F229" s="41"/>
-      <x:c r="G229" s="41"/>
-      <x:c r="H229" s="41"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A230" s="41"/>
-      <x:c r="B230" s="41"/>
-      <x:c r="C230" s="41"/>
-      <x:c r="D230" s="41"/>
-      <x:c r="E230" s="41"/>
-      <x:c r="F230" s="41"/>
-      <x:c r="G230" s="41"/>
-      <x:c r="H230" s="41"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A231" s="41"/>
-      <x:c r="B231" s="41"/>
-      <x:c r="C231" s="41"/>
-      <x:c r="D231" s="41"/>
-      <x:c r="E231" s="41"/>
-      <x:c r="F231" s="41"/>
-      <x:c r="G231" s="41"/>
-      <x:c r="H231" s="41"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A232" s="41"/>
-      <x:c r="B232" s="41"/>
-      <x:c r="C232" s="41"/>
-      <x:c r="D232" s="41"/>
-      <x:c r="E232" s="41"/>
-      <x:c r="F232" s="41"/>
-      <x:c r="G232" s="41"/>
-      <x:c r="H232" s="41"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A233" s="41"/>
-      <x:c r="B233" s="41"/>
-      <x:c r="C233" s="41"/>
-      <x:c r="D233" s="41"/>
-      <x:c r="E233" s="41"/>
-      <x:c r="F233" s="41"/>
-      <x:c r="G233" s="41"/>
-      <x:c r="H233" s="41"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A234" s="41"/>
-      <x:c r="B234" s="41"/>
-      <x:c r="C234" s="41"/>
-      <x:c r="D234" s="41"/>
-      <x:c r="E234" s="41"/>
-      <x:c r="F234" s="41"/>
-      <x:c r="G234" s="41"/>
-      <x:c r="H234" s="41"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A235" s="41"/>
-      <x:c r="B235" s="41"/>
-      <x:c r="C235" s="41"/>
-      <x:c r="D235" s="41"/>
-      <x:c r="E235" s="41"/>
-      <x:c r="F235" s="41"/>
-      <x:c r="G235" s="41"/>
-      <x:c r="H235" s="41"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A236" s="41"/>
-      <x:c r="B236" s="41"/>
-      <x:c r="C236" s="41"/>
-      <x:c r="D236" s="41"/>
-      <x:c r="E236" s="41"/>
-      <x:c r="F236" s="41"/>
-      <x:c r="G236" s="41"/>
-      <x:c r="H236" s="41"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A237" s="41"/>
-      <x:c r="B237" s="41"/>
-      <x:c r="C237" s="41"/>
-      <x:c r="D237" s="41"/>
-      <x:c r="E237" s="41"/>
-      <x:c r="F237" s="41"/>
-      <x:c r="G237" s="41"/>
-      <x:c r="H237" s="41"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A238" s="42"/>
-      <x:c r="B238" s="42"/>
-      <x:c r="C238" s="42"/>
-      <x:c r="D238" s="42"/>
-      <x:c r="E238" s="42"/>
-      <x:c r="F238" s="42"/>
-      <x:c r="G238" s="42"/>
-      <x:c r="H238" s="42"/>
+      <x:c r="A28" s="47" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B28" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="C28" s="47"/>
+      <x:c r="D28" s="47"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="47"/>
+      <x:c r="G28" s="47"/>
+      <x:c r="H28" s="47"/>
+      <x:c r="I28" s="47"/>
+      <x:c r="J28" s="47"/>
+      <x:c r="K28" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10048,19 +8478,22 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Project Execution</x:v>
+        <x:v>FY27 signed-backlog execution | priority and earnings</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -10069,10 +8502,13 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
+        <x:v>Use approved customer priority and contract terms; roll unfinished work rather than manufacturing capacity</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -10081,2343 +8517,325 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Project</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Signed backlog</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Completed hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Deferred hours</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Completed revenue</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Deferred revenue</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>Completed gross profit</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Liquidated damages</x:v>
+      </x:c>
+      <x:c r="K4" s="17" t="str">
+        <x:v>Release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>execution_2026_07_available_hours</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="45" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="B5" s="45"/>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
+      <x:c r="J5" s="45"/>
+      <x:c r="K5" s="45"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>execution_2026_07_due_hours</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="46" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="B6" s="46"/>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
+      <x:c r="J6" s="46"/>
+      <x:c r="K6" s="46"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>execution_2026_07_completed_hours</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="46" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="B7" s="46"/>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
+      <x:c r="J7" s="46"/>
+      <x:c r="K7" s="46"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>execution_2026_07_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="46" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="B8" s="46"/>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
+      <x:c r="J8" s="46"/>
+      <x:c r="K8" s="46"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>execution_2026_07_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="46" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+      <x:c r="J9" s="46"/>
+      <x:c r="K9" s="46"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>execution_2026_07_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="46" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="B10" s="46"/>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
+      <x:c r="J10" s="46"/>
+      <x:c r="K10" s="46"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>execution_2026_07_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="46" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
+      <x:c r="J11" s="46"/>
+      <x:c r="K11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>execution_2026_07_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B12" s="36"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>execution_2026_07_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B13" s="36"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>execution_2026_07_release_status</x:v>
-      </x:c>
-      <x:c r="B14" s="36"/>
+      <x:c r="A12" s="47" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="B12" s="47"/>
+      <x:c r="C12" s="47"/>
+      <x:c r="D12" s="47"/>
+      <x:c r="E12" s="47"/>
+      <x:c r="F12" s="47"/>
+      <x:c r="G12" s="47"/>
+      <x:c r="H12" s="47"/>
+      <x:c r="I12" s="47"/>
+      <x:c r="J12" s="47"/>
+      <x:c r="K12" s="47"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>release_bridge_2026_07_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B15" s="36"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>release_bridge_2026_07_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B16" s="36"/>
+      <x:c r="A15" s="48" t="str">
+        <x:v>MONTHLY EARNINGS RELEASE BRIDGE</x:v>
+      </x:c>
+      <x:c r="B15" s="48"/>
+      <x:c r="C15" s="48"/>
+      <x:c r="D15" s="48"/>
+      <x:c r="E15" s="48"/>
+      <x:c r="F15" s="48"/>
+      <x:c r="G15" s="48"/>
+      <x:c r="H15" s="48"/>
+      <x:c r="I15" s="48"/>
+      <x:c r="J15" s="48"/>
+      <x:c r="K15" s="48"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Probability-plan GP after response</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>Gross-commitment GP after response</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>Executable GP after damages</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>Deferred revenue at risk</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>Management decision</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>release_bridge_2026_07_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B17" s="36"/>
+      <x:c r="A17" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B17" s="45"/>
+      <x:c r="C17" s="45"/>
+      <x:c r="D17" s="45"/>
+      <x:c r="E17" s="45"/>
+      <x:c r="F17" s="45"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>release_bridge_2026_07_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B18" s="36"/>
+      <x:c r="A18" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B18" s="46"/>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>release_bridge_2026_07_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B19" s="36"/>
+      <x:c r="A19" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B19" s="46"/>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>release_bridge_2026_07_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B20" s="36"/>
+      <x:c r="A20" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B20" s="46"/>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>release_bridge_2026_07_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B21" s="36"/>
+      <x:c r="A21" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B21" s="46"/>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="46"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>release_bridge_2026_07_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B22" s="36"/>
+      <x:c r="A22" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B22" s="46"/>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="46"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>release_bridge_2026_07_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B23" s="36"/>
+      <x:c r="A23" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B23" s="46"/>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="46"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>release_bridge_2026_07_management_release_status</x:v>
-      </x:c>
-      <x:c r="B24" s="36"/>
+      <x:c r="A24" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B24" s="46"/>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="46"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>execution_2026_08_available_hours</x:v>
-      </x:c>
-      <x:c r="B25" s="36"/>
+      <x:c r="A25" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B25" s="46"/>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>execution_2026_08_due_hours</x:v>
-      </x:c>
-      <x:c r="B26" s="36"/>
+      <x:c r="A26" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B26" s="46"/>
+      <x:c r="C26" s="46"/>
+      <x:c r="D26" s="46"/>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="46"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>execution_2026_08_completed_hours</x:v>
-      </x:c>
-      <x:c r="B27" s="36"/>
+      <x:c r="A27" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B27" s="46"/>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="46"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>execution_2026_08_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B28" s="36"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="33" t="str">
-        <x:v>execution_2026_08_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B29" s="36"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="33" t="str">
-        <x:v>execution_2026_08_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B30" s="36"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="33" t="str">
-        <x:v>execution_2026_08_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B31" s="36"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="33" t="str">
-        <x:v>execution_2026_08_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B32" s="36"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="33" t="str">
-        <x:v>execution_2026_08_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B33" s="36"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="33" t="str">
-        <x:v>execution_2026_08_release_status</x:v>
-      </x:c>
-      <x:c r="B34" s="36"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="33" t="str">
-        <x:v>release_bridge_2026_08_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B35" s="36"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="33" t="str">
-        <x:v>release_bridge_2026_08_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B36" s="36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="33" t="str">
-        <x:v>release_bridge_2026_08_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B37" s="36"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="33" t="str">
-        <x:v>release_bridge_2026_08_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B38" s="36"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="33" t="str">
-        <x:v>release_bridge_2026_08_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B39" s="36"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="33" t="str">
-        <x:v>release_bridge_2026_08_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B40" s="36"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="33" t="str">
-        <x:v>release_bridge_2026_08_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B41" s="36"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="33" t="str">
-        <x:v>release_bridge_2026_08_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B42" s="36"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="33" t="str">
-        <x:v>release_bridge_2026_08_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B43" s="36"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="33" t="str">
-        <x:v>release_bridge_2026_08_management_release_status</x:v>
-      </x:c>
-      <x:c r="B44" s="36"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="33" t="str">
-        <x:v>execution_2026_09_available_hours</x:v>
-      </x:c>
-      <x:c r="B45" s="36"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="33" t="str">
-        <x:v>execution_2026_09_due_hours</x:v>
-      </x:c>
-      <x:c r="B46" s="36"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="33" t="str">
-        <x:v>execution_2026_09_completed_hours</x:v>
-      </x:c>
-      <x:c r="B47" s="36"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="33" t="str">
-        <x:v>execution_2026_09_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B48" s="36"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="33" t="str">
-        <x:v>execution_2026_09_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B49" s="36"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="33" t="str">
-        <x:v>execution_2026_09_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B50" s="36"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="33" t="str">
-        <x:v>execution_2026_09_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B51" s="36"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="33" t="str">
-        <x:v>execution_2026_09_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B52" s="36"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="33" t="str">
-        <x:v>execution_2026_09_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B53" s="36"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="33" t="str">
-        <x:v>execution_2026_09_release_status</x:v>
-      </x:c>
-      <x:c r="B54" s="36"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="33" t="str">
-        <x:v>release_bridge_2026_09_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B55" s="36"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="33" t="str">
-        <x:v>release_bridge_2026_09_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B56" s="36"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="33" t="str">
-        <x:v>release_bridge_2026_09_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B57" s="36"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="33" t="str">
-        <x:v>release_bridge_2026_09_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B58" s="36"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="33" t="str">
-        <x:v>release_bridge_2026_09_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B59" s="36"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="33" t="str">
-        <x:v>release_bridge_2026_09_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B60" s="36"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="33" t="str">
-        <x:v>release_bridge_2026_09_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B61" s="36"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="33" t="str">
-        <x:v>release_bridge_2026_09_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B62" s="36"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="33" t="str">
-        <x:v>release_bridge_2026_09_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B63" s="36"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="33" t="str">
-        <x:v>release_bridge_2026_09_management_release_status</x:v>
-      </x:c>
-      <x:c r="B64" s="36"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="33" t="str">
-        <x:v>execution_2026_10_available_hours</x:v>
-      </x:c>
-      <x:c r="B65" s="36"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="33" t="str">
-        <x:v>execution_2026_10_due_hours</x:v>
-      </x:c>
-      <x:c r="B66" s="36"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="33" t="str">
-        <x:v>execution_2026_10_completed_hours</x:v>
-      </x:c>
-      <x:c r="B67" s="36"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="33" t="str">
-        <x:v>execution_2026_10_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B68" s="36"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="33" t="str">
-        <x:v>execution_2026_10_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B69" s="36"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="33" t="str">
-        <x:v>execution_2026_10_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B70" s="36"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="33" t="str">
-        <x:v>execution_2026_10_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B71" s="36"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="33" t="str">
-        <x:v>execution_2026_10_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B72" s="36"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="33" t="str">
-        <x:v>execution_2026_10_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B73" s="36"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="33" t="str">
-        <x:v>execution_2026_10_release_status</x:v>
-      </x:c>
-      <x:c r="B74" s="36"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="33" t="str">
-        <x:v>release_bridge_2026_10_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B75" s="36"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="33" t="str">
-        <x:v>release_bridge_2026_10_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B76" s="36"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="33" t="str">
-        <x:v>release_bridge_2026_10_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B77" s="36"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="33" t="str">
-        <x:v>release_bridge_2026_10_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B78" s="36"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="33" t="str">
-        <x:v>release_bridge_2026_10_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B79" s="36"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="33" t="str">
-        <x:v>release_bridge_2026_10_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B80" s="36"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="33" t="str">
-        <x:v>release_bridge_2026_10_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B81" s="36"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="33" t="str">
-        <x:v>release_bridge_2026_10_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B82" s="36"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="33" t="str">
-        <x:v>release_bridge_2026_10_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B83" s="36"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="33" t="str">
-        <x:v>release_bridge_2026_10_management_release_status</x:v>
-      </x:c>
-      <x:c r="B84" s="36"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="33" t="str">
-        <x:v>execution_2026_11_available_hours</x:v>
-      </x:c>
-      <x:c r="B85" s="36"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="33" t="str">
-        <x:v>execution_2026_11_due_hours</x:v>
-      </x:c>
-      <x:c r="B86" s="36"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="33" t="str">
-        <x:v>execution_2026_11_completed_hours</x:v>
-      </x:c>
-      <x:c r="B87" s="36"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="33" t="str">
-        <x:v>execution_2026_11_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B88" s="36"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="33" t="str">
-        <x:v>execution_2026_11_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B89" s="36"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="33" t="str">
-        <x:v>execution_2026_11_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B90" s="36"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="33" t="str">
-        <x:v>execution_2026_11_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B91" s="36"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92" s="33" t="str">
-        <x:v>execution_2026_11_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B92" s="36"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93" s="33" t="str">
-        <x:v>execution_2026_11_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B93" s="36"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="33" t="str">
-        <x:v>execution_2026_11_release_status</x:v>
-      </x:c>
-      <x:c r="B94" s="36"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="33" t="str">
-        <x:v>release_bridge_2026_11_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B95" s="36"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="33" t="str">
-        <x:v>release_bridge_2026_11_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B96" s="36"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="33" t="str">
-        <x:v>release_bridge_2026_11_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B97" s="36"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="33" t="str">
-        <x:v>release_bridge_2026_11_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B98" s="36"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="33" t="str">
-        <x:v>release_bridge_2026_11_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B99" s="36"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="33" t="str">
-        <x:v>release_bridge_2026_11_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B100" s="36"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="33" t="str">
-        <x:v>release_bridge_2026_11_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B101" s="36"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="33" t="str">
-        <x:v>release_bridge_2026_11_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B102" s="36"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="33" t="str">
-        <x:v>release_bridge_2026_11_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B103" s="36"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="33" t="str">
-        <x:v>release_bridge_2026_11_management_release_status</x:v>
-      </x:c>
-      <x:c r="B104" s="36"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="33" t="str">
-        <x:v>execution_2026_12_available_hours</x:v>
-      </x:c>
-      <x:c r="B105" s="36"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="33" t="str">
-        <x:v>execution_2026_12_due_hours</x:v>
-      </x:c>
-      <x:c r="B106" s="36"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="33" t="str">
-        <x:v>execution_2026_12_completed_hours</x:v>
-      </x:c>
-      <x:c r="B107" s="36"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="33" t="str">
-        <x:v>execution_2026_12_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B108" s="36"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="A109" s="33" t="str">
-        <x:v>execution_2026_12_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B109" s="36"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="33" t="str">
-        <x:v>execution_2026_12_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B110" s="36"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="33" t="str">
-        <x:v>execution_2026_12_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B111" s="36"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="A112" s="33" t="str">
-        <x:v>execution_2026_12_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B112" s="36"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="A113" s="33" t="str">
-        <x:v>execution_2026_12_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B113" s="36"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="33" t="str">
-        <x:v>execution_2026_12_release_status</x:v>
-      </x:c>
-      <x:c r="B114" s="36"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="33" t="str">
-        <x:v>release_bridge_2026_12_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B115" s="36"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="33" t="str">
-        <x:v>release_bridge_2026_12_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B116" s="36"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="33" t="str">
-        <x:v>release_bridge_2026_12_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B117" s="36"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="33" t="str">
-        <x:v>release_bridge_2026_12_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B118" s="36"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="A119" s="33" t="str">
-        <x:v>release_bridge_2026_12_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B119" s="36"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="A120" s="33" t="str">
-        <x:v>release_bridge_2026_12_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B120" s="36"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="A121" s="33" t="str">
-        <x:v>release_bridge_2026_12_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B121" s="36"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="A122" s="33" t="str">
-        <x:v>release_bridge_2026_12_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B122" s="36"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="A123" s="33" t="str">
-        <x:v>release_bridge_2026_12_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B123" s="36"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="A124" s="33" t="str">
-        <x:v>release_bridge_2026_12_management_release_status</x:v>
-      </x:c>
-      <x:c r="B124" s="36"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="A125" s="33" t="str">
-        <x:v>execution_2027_01_available_hours</x:v>
-      </x:c>
-      <x:c r="B125" s="36"/>
-    </x:row>
-    <x:row r="126">
-      <x:c r="A126" s="33" t="str">
-        <x:v>execution_2027_01_due_hours</x:v>
-      </x:c>
-      <x:c r="B126" s="36"/>
-    </x:row>
-    <x:row r="127">
-      <x:c r="A127" s="33" t="str">
-        <x:v>execution_2027_01_completed_hours</x:v>
-      </x:c>
-      <x:c r="B127" s="36"/>
-    </x:row>
-    <x:row r="128">
-      <x:c r="A128" s="33" t="str">
-        <x:v>execution_2027_01_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B128" s="36"/>
-    </x:row>
-    <x:row r="129">
-      <x:c r="A129" s="33" t="str">
-        <x:v>execution_2027_01_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B129" s="36"/>
-    </x:row>
-    <x:row r="130">
-      <x:c r="A130" s="33" t="str">
-        <x:v>execution_2027_01_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B130" s="36"/>
-    </x:row>
-    <x:row r="131">
-      <x:c r="A131" s="33" t="str">
-        <x:v>execution_2027_01_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B131" s="36"/>
-    </x:row>
-    <x:row r="132">
-      <x:c r="A132" s="33" t="str">
-        <x:v>execution_2027_01_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B132" s="36"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="A133" s="33" t="str">
-        <x:v>execution_2027_01_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B133" s="36"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="33" t="str">
-        <x:v>execution_2027_01_release_status</x:v>
-      </x:c>
-      <x:c r="B134" s="36"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="33" t="str">
-        <x:v>release_bridge_2027_01_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B135" s="36"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="33" t="str">
-        <x:v>release_bridge_2027_01_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B136" s="36"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="33" t="str">
-        <x:v>release_bridge_2027_01_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B137" s="36"/>
-    </x:row>
-    <x:row r="138">
-      <x:c r="A138" s="33" t="str">
-        <x:v>release_bridge_2027_01_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B138" s="36"/>
-    </x:row>
-    <x:row r="139">
-      <x:c r="A139" s="33" t="str">
-        <x:v>release_bridge_2027_01_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B139" s="36"/>
-    </x:row>
-    <x:row r="140">
-      <x:c r="A140" s="33" t="str">
-        <x:v>release_bridge_2027_01_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B140" s="36"/>
-    </x:row>
-    <x:row r="141">
-      <x:c r="A141" s="33" t="str">
-        <x:v>release_bridge_2027_01_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B141" s="36"/>
-    </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="33" t="str">
-        <x:v>release_bridge_2027_01_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B142" s="36"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="33" t="str">
-        <x:v>release_bridge_2027_01_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B143" s="36"/>
-    </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="33" t="str">
-        <x:v>release_bridge_2027_01_management_release_status</x:v>
-      </x:c>
-      <x:c r="B144" s="36"/>
-    </x:row>
-    <x:row r="145">
-      <x:c r="A145" s="33" t="str">
-        <x:v>execution_2027_02_available_hours</x:v>
-      </x:c>
-      <x:c r="B145" s="36"/>
-    </x:row>
-    <x:row r="146">
-      <x:c r="A146" s="33" t="str">
-        <x:v>execution_2027_02_due_hours</x:v>
-      </x:c>
-      <x:c r="B146" s="36"/>
-    </x:row>
-    <x:row r="147">
-      <x:c r="A147" s="33" t="str">
-        <x:v>execution_2027_02_completed_hours</x:v>
-      </x:c>
-      <x:c r="B147" s="36"/>
-    </x:row>
-    <x:row r="148">
-      <x:c r="A148" s="33" t="str">
-        <x:v>execution_2027_02_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B148" s="36"/>
-    </x:row>
-    <x:row r="149">
-      <x:c r="A149" s="33" t="str">
-        <x:v>execution_2027_02_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B149" s="36"/>
-    </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="33" t="str">
-        <x:v>execution_2027_02_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B150" s="36"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="33" t="str">
-        <x:v>execution_2027_02_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B151" s="36"/>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="33" t="str">
-        <x:v>execution_2027_02_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B152" s="36"/>
-    </x:row>
-    <x:row r="153">
-      <x:c r="A153" s="33" t="str">
-        <x:v>execution_2027_02_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B153" s="36"/>
-    </x:row>
-    <x:row r="154">
-      <x:c r="A154" s="33" t="str">
-        <x:v>execution_2027_02_release_status</x:v>
-      </x:c>
-      <x:c r="B154" s="36"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="33" t="str">
-        <x:v>release_bridge_2027_02_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B155" s="36"/>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156" s="33" t="str">
-        <x:v>release_bridge_2027_02_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B156" s="36"/>
-    </x:row>
-    <x:row r="157">
-      <x:c r="A157" s="33" t="str">
-        <x:v>release_bridge_2027_02_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B157" s="36"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="33" t="str">
-        <x:v>release_bridge_2027_02_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B158" s="36"/>
-    </x:row>
-    <x:row r="159">
-      <x:c r="A159" s="33" t="str">
-        <x:v>release_bridge_2027_02_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B159" s="36"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="33" t="str">
-        <x:v>release_bridge_2027_02_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B160" s="36"/>
-    </x:row>
-    <x:row r="161">
-      <x:c r="A161" s="33" t="str">
-        <x:v>release_bridge_2027_02_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B161" s="36"/>
-    </x:row>
-    <x:row r="162">
-      <x:c r="A162" s="33" t="str">
-        <x:v>release_bridge_2027_02_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B162" s="36"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" s="33" t="str">
-        <x:v>release_bridge_2027_02_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B163" s="36"/>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164" s="33" t="str">
-        <x:v>release_bridge_2027_02_management_release_status</x:v>
-      </x:c>
-      <x:c r="B164" s="36"/>
-    </x:row>
-    <x:row r="165">
-      <x:c r="A165" s="33" t="str">
-        <x:v>execution_2027_03_available_hours</x:v>
-      </x:c>
-      <x:c r="B165" s="36"/>
-    </x:row>
-    <x:row r="166">
-      <x:c r="A166" s="33" t="str">
-        <x:v>execution_2027_03_due_hours</x:v>
-      </x:c>
-      <x:c r="B166" s="36"/>
-    </x:row>
-    <x:row r="167">
-      <x:c r="A167" s="33" t="str">
-        <x:v>execution_2027_03_completed_hours</x:v>
-      </x:c>
-      <x:c r="B167" s="36"/>
-    </x:row>
-    <x:row r="168">
-      <x:c r="A168" s="33" t="str">
-        <x:v>execution_2027_03_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B168" s="36"/>
-    </x:row>
-    <x:row r="169">
-      <x:c r="A169" s="33" t="str">
-        <x:v>execution_2027_03_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B169" s="36"/>
-    </x:row>
-    <x:row r="170">
-      <x:c r="A170" s="33" t="str">
-        <x:v>execution_2027_03_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B170" s="36"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171" s="33" t="str">
-        <x:v>execution_2027_03_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B171" s="36"/>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172" s="33" t="str">
-        <x:v>execution_2027_03_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B172" s="36"/>
-    </x:row>
-    <x:row r="173">
-      <x:c r="A173" s="33" t="str">
-        <x:v>execution_2027_03_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B173" s="36"/>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174" s="33" t="str">
-        <x:v>execution_2027_03_release_status</x:v>
-      </x:c>
-      <x:c r="B174" s="36"/>
-    </x:row>
-    <x:row r="175">
-      <x:c r="A175" s="33" t="str">
-        <x:v>release_bridge_2027_03_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B175" s="36"/>
-    </x:row>
-    <x:row r="176">
-      <x:c r="A176" s="33" t="str">
-        <x:v>release_bridge_2027_03_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B176" s="36"/>
-    </x:row>
-    <x:row r="177">
-      <x:c r="A177" s="33" t="str">
-        <x:v>release_bridge_2027_03_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B177" s="36"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178" s="33" t="str">
-        <x:v>release_bridge_2027_03_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B178" s="36"/>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179" s="33" t="str">
-        <x:v>release_bridge_2027_03_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B179" s="36"/>
-    </x:row>
-    <x:row r="180">
-      <x:c r="A180" s="33" t="str">
-        <x:v>release_bridge_2027_03_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B180" s="36"/>
-    </x:row>
-    <x:row r="181">
-      <x:c r="A181" s="33" t="str">
-        <x:v>release_bridge_2027_03_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B181" s="36"/>
-    </x:row>
-    <x:row r="182">
-      <x:c r="A182" s="33" t="str">
-        <x:v>release_bridge_2027_03_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B182" s="36"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="33" t="str">
-        <x:v>release_bridge_2027_03_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B183" s="36"/>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="33" t="str">
-        <x:v>release_bridge_2027_03_management_release_status</x:v>
-      </x:c>
-      <x:c r="B184" s="36"/>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185" s="33" t="str">
-        <x:v>execution_2027_04_available_hours</x:v>
-      </x:c>
-      <x:c r="B185" s="36"/>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186" s="33" t="str">
-        <x:v>execution_2027_04_due_hours</x:v>
-      </x:c>
-      <x:c r="B186" s="36"/>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187" s="33" t="str">
-        <x:v>execution_2027_04_completed_hours</x:v>
-      </x:c>
-      <x:c r="B187" s="36"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" s="33" t="str">
-        <x:v>execution_2027_04_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B188" s="36"/>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" s="33" t="str">
-        <x:v>execution_2027_04_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B189" s="36"/>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190" s="33" t="str">
-        <x:v>execution_2027_04_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B190" s="36"/>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191" s="33" t="str">
-        <x:v>execution_2027_04_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B191" s="36"/>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192" s="33" t="str">
-        <x:v>execution_2027_04_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B192" s="36"/>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193" s="33" t="str">
-        <x:v>execution_2027_04_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B193" s="36"/>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194" s="33" t="str">
-        <x:v>execution_2027_04_release_status</x:v>
-      </x:c>
-      <x:c r="B194" s="36"/>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195" s="33" t="str">
-        <x:v>release_bridge_2027_04_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B195" s="36"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" s="33" t="str">
-        <x:v>release_bridge_2027_04_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B196" s="36"/>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" s="33" t="str">
-        <x:v>release_bridge_2027_04_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B197" s="36"/>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198" s="33" t="str">
-        <x:v>release_bridge_2027_04_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B198" s="36"/>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" s="33" t="str">
-        <x:v>release_bridge_2027_04_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B199" s="36"/>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200" s="33" t="str">
-        <x:v>release_bridge_2027_04_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B200" s="36"/>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201" s="33" t="str">
-        <x:v>release_bridge_2027_04_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B201" s="36"/>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202" s="33" t="str">
-        <x:v>release_bridge_2027_04_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B202" s="36"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203" s="33" t="str">
-        <x:v>release_bridge_2027_04_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B203" s="36"/>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204" s="33" t="str">
-        <x:v>release_bridge_2027_04_management_release_status</x:v>
-      </x:c>
-      <x:c r="B204" s="36"/>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A205" s="33" t="str">
-        <x:v>execution_2027_05_available_hours</x:v>
-      </x:c>
-      <x:c r="B205" s="36"/>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A206" s="33" t="str">
-        <x:v>execution_2027_05_due_hours</x:v>
-      </x:c>
-      <x:c r="B206" s="36"/>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A207" s="33" t="str">
-        <x:v>execution_2027_05_completed_hours</x:v>
-      </x:c>
-      <x:c r="B207" s="36"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208" s="33" t="str">
-        <x:v>execution_2027_05_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B208" s="36"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="33" t="str">
-        <x:v>execution_2027_05_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B209" s="36"/>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A210" s="33" t="str">
-        <x:v>execution_2027_05_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B210" s="36"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="33" t="str">
-        <x:v>execution_2027_05_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B211" s="36"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" s="33" t="str">
-        <x:v>execution_2027_05_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B212" s="36"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" s="33" t="str">
-        <x:v>execution_2027_05_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B213" s="36"/>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" s="33" t="str">
-        <x:v>execution_2027_05_release_status</x:v>
-      </x:c>
-      <x:c r="B214" s="36"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A215" s="33" t="str">
-        <x:v>release_bridge_2027_05_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B215" s="36"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A216" s="33" t="str">
-        <x:v>release_bridge_2027_05_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B216" s="36"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A217" s="33" t="str">
-        <x:v>release_bridge_2027_05_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B217" s="36"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="A218" s="33" t="str">
-        <x:v>release_bridge_2027_05_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B218" s="36"/>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A219" s="33" t="str">
-        <x:v>release_bridge_2027_05_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B219" s="36"/>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A220" s="33" t="str">
-        <x:v>release_bridge_2027_05_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B220" s="36"/>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="33" t="str">
-        <x:v>release_bridge_2027_05_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B221" s="36"/>
-    </x:row>
-    <x:row r="222">
-      <x:c r="A222" s="33" t="str">
-        <x:v>release_bridge_2027_05_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B222" s="36"/>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A223" s="33" t="str">
-        <x:v>release_bridge_2027_05_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B223" s="36"/>
-    </x:row>
-    <x:row r="224">
-      <x:c r="A224" s="33" t="str">
-        <x:v>release_bridge_2027_05_management_release_status</x:v>
-      </x:c>
-      <x:c r="B224" s="36"/>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A225" s="33" t="str">
-        <x:v>execution_2027_06_available_hours</x:v>
-      </x:c>
-      <x:c r="B225" s="36"/>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A226" s="33" t="str">
-        <x:v>execution_2027_06_due_hours</x:v>
-      </x:c>
-      <x:c r="B226" s="36"/>
-    </x:row>
-    <x:row r="227">
-      <x:c r="A227" s="33" t="str">
-        <x:v>execution_2027_06_completed_hours</x:v>
-      </x:c>
-      <x:c r="B227" s="36"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A228" s="33" t="str">
-        <x:v>execution_2027_06_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B228" s="36"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229" s="33" t="str">
-        <x:v>execution_2027_06_capacity_utilization</x:v>
-      </x:c>
-      <x:c r="B229" s="36"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A230" s="33" t="str">
-        <x:v>execution_2027_06_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B230" s="36"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A231" s="33" t="str">
-        <x:v>execution_2027_06_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B231" s="36"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A232" s="33" t="str">
-        <x:v>execution_2027_06_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B232" s="36"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A233" s="33" t="str">
-        <x:v>execution_2027_06_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B233" s="36"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A234" s="33" t="str">
-        <x:v>execution_2027_06_release_status</x:v>
-      </x:c>
-      <x:c r="B234" s="36"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A235" s="33" t="str">
-        <x:v>release_bridge_2027_06_probability_plan_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B235" s="36"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A236" s="33" t="str">
-        <x:v>release_bridge_2027_06_probability_plan_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B236" s="36"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A237" s="33" t="str">
-        <x:v>release_bridge_2027_06_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B237" s="36"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A238" s="33" t="str">
-        <x:v>release_bridge_2027_06_gross_commitment_gross_profit_before_remediation</x:v>
-      </x:c>
-      <x:c r="B238" s="36"/>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A239" s="33" t="str">
-        <x:v>release_bridge_2027_06_gross_commitment_remediation_cost</x:v>
-      </x:c>
-      <x:c r="B239" s="36"/>
-    </x:row>
-    <x:row r="240">
-      <x:c r="A240" s="33" t="str">
-        <x:v>release_bridge_2027_06_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B240" s="36"/>
-    </x:row>
-    <x:row r="241">
-      <x:c r="A241" s="33" t="str">
-        <x:v>release_bridge_2027_06_incremental_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B241" s="36"/>
-    </x:row>
-    <x:row r="242">
-      <x:c r="A242" s="33" t="str">
-        <x:v>release_bridge_2027_06_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B242" s="36"/>
-    </x:row>
-    <x:row r="243">
-      <x:c r="A243" s="33" t="str">
-        <x:v>release_bridge_2027_06_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B243" s="36"/>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A244" s="33" t="str">
-        <x:v>release_bridge_2027_06_management_release_status</x:v>
-      </x:c>
-      <x:c r="B244" s="36"/>
-    </x:row>
-    <x:row r="245">
-      <x:c r="A245" s="33" t="str">
-        <x:v>execution_p_3114_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B245" s="36"/>
-    </x:row>
-    <x:row r="246">
-      <x:c r="A246" s="33" t="str">
-        <x:v>execution_p_3114_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B246" s="36"/>
-    </x:row>
-    <x:row r="247">
-      <x:c r="A247" s="33" t="str">
-        <x:v>execution_p_3114_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B247" s="36"/>
-    </x:row>
-    <x:row r="248">
-      <x:c r="A248" s="33" t="str">
-        <x:v>execution_p_3114_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B248" s="36"/>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A249" s="33" t="str">
-        <x:v>execution_p_3114_completed_hours</x:v>
-      </x:c>
-      <x:c r="B249" s="36"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250" s="33" t="str">
-        <x:v>execution_p_3114_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B250" s="36"/>
-    </x:row>
-    <x:row r="251">
-      <x:c r="A251" s="33" t="str">
-        <x:v>execution_p_3114_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B251" s="36"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252" s="33" t="str">
-        <x:v>execution_p_3114_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B252" s="36"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253" s="33" t="str">
-        <x:v>execution_p_3114_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B253" s="36"/>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254" s="33" t="str">
-        <x:v>execution_p_3114_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B254" s="36"/>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255" s="33" t="str">
-        <x:v>execution_p_3114_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B255" s="36"/>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256" s="33" t="str">
-        <x:v>execution_p_3114_release_status</x:v>
-      </x:c>
-      <x:c r="B256" s="36"/>
-    </x:row>
-    <x:row r="257">
-      <x:c r="A257" s="33" t="str">
-        <x:v>execution_p_3101_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B257" s="36"/>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A258" s="33" t="str">
-        <x:v>execution_p_3101_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B258" s="36"/>
-    </x:row>
-    <x:row r="259">
-      <x:c r="A259" s="33" t="str">
-        <x:v>execution_p_3101_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B259" s="36"/>
-    </x:row>
-    <x:row r="260">
-      <x:c r="A260" s="33" t="str">
-        <x:v>execution_p_3101_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B260" s="36"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A261" s="33" t="str">
-        <x:v>execution_p_3101_completed_hours</x:v>
-      </x:c>
-      <x:c r="B261" s="36"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262" s="33" t="str">
-        <x:v>execution_p_3101_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B262" s="36"/>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A263" s="33" t="str">
-        <x:v>execution_p_3101_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B263" s="36"/>
-    </x:row>
-    <x:row r="264">
-      <x:c r="A264" s="33" t="str">
-        <x:v>execution_p_3101_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B264" s="36"/>
-    </x:row>
-    <x:row r="265">
-      <x:c r="A265" s="33" t="str">
-        <x:v>execution_p_3101_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B265" s="36"/>
-    </x:row>
-    <x:row r="266">
-      <x:c r="A266" s="33" t="str">
-        <x:v>execution_p_3101_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B266" s="36"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A267" s="33" t="str">
-        <x:v>execution_p_3101_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B267" s="36"/>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A268" s="33" t="str">
-        <x:v>execution_p_3101_release_status</x:v>
-      </x:c>
-      <x:c r="B268" s="36"/>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A269" s="33" t="str">
-        <x:v>execution_p_3130_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B269" s="36"/>
-    </x:row>
-    <x:row r="270">
-      <x:c r="A270" s="33" t="str">
-        <x:v>execution_p_3130_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B270" s="36"/>
-    </x:row>
-    <x:row r="271">
-      <x:c r="A271" s="33" t="str">
-        <x:v>execution_p_3130_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B271" s="36"/>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A272" s="33" t="str">
-        <x:v>execution_p_3130_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B272" s="36"/>
-    </x:row>
-    <x:row r="273">
-      <x:c r="A273" s="33" t="str">
-        <x:v>execution_p_3130_completed_hours</x:v>
-      </x:c>
-      <x:c r="B273" s="36"/>
-    </x:row>
-    <x:row r="274">
-      <x:c r="A274" s="33" t="str">
-        <x:v>execution_p_3130_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B274" s="36"/>
-    </x:row>
-    <x:row r="275">
-      <x:c r="A275" s="33" t="str">
-        <x:v>execution_p_3130_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B275" s="36"/>
-    </x:row>
-    <x:row r="276">
-      <x:c r="A276" s="33" t="str">
-        <x:v>execution_p_3130_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B276" s="36"/>
-    </x:row>
-    <x:row r="277">
-      <x:c r="A277" s="33" t="str">
-        <x:v>execution_p_3130_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B277" s="36"/>
-    </x:row>
-    <x:row r="278">
-      <x:c r="A278" s="33" t="str">
-        <x:v>execution_p_3130_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B278" s="36"/>
-    </x:row>
-    <x:row r="279">
-      <x:c r="A279" s="33" t="str">
-        <x:v>execution_p_3130_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B279" s="36"/>
-    </x:row>
-    <x:row r="280">
-      <x:c r="A280" s="33" t="str">
-        <x:v>execution_p_3130_release_status</x:v>
-      </x:c>
-      <x:c r="B280" s="36"/>
-    </x:row>
-    <x:row r="281">
-      <x:c r="A281" s="33" t="str">
-        <x:v>execution_p_3107_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B281" s="36"/>
-    </x:row>
-    <x:row r="282">
-      <x:c r="A282" s="33" t="str">
-        <x:v>execution_p_3107_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B282" s="36"/>
-    </x:row>
-    <x:row r="283">
-      <x:c r="A283" s="33" t="str">
-        <x:v>execution_p_3107_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B283" s="36"/>
-    </x:row>
-    <x:row r="284">
-      <x:c r="A284" s="33" t="str">
-        <x:v>execution_p_3107_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B284" s="36"/>
-    </x:row>
-    <x:row r="285">
-      <x:c r="A285" s="33" t="str">
-        <x:v>execution_p_3107_completed_hours</x:v>
-      </x:c>
-      <x:c r="B285" s="36"/>
-    </x:row>
-    <x:row r="286">
-      <x:c r="A286" s="33" t="str">
-        <x:v>execution_p_3107_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B286" s="36"/>
-    </x:row>
-    <x:row r="287">
-      <x:c r="A287" s="33" t="str">
-        <x:v>execution_p_3107_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B287" s="36"/>
-    </x:row>
-    <x:row r="288">
-      <x:c r="A288" s="33" t="str">
-        <x:v>execution_p_3107_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B288" s="36"/>
-    </x:row>
-    <x:row r="289">
-      <x:c r="A289" s="33" t="str">
-        <x:v>execution_p_3107_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B289" s="36"/>
-    </x:row>
-    <x:row r="290">
-      <x:c r="A290" s="33" t="str">
-        <x:v>execution_p_3107_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B290" s="36"/>
-    </x:row>
-    <x:row r="291">
-      <x:c r="A291" s="33" t="str">
-        <x:v>execution_p_3107_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B291" s="36"/>
-    </x:row>
-    <x:row r="292">
-      <x:c r="A292" s="33" t="str">
-        <x:v>execution_p_3107_release_status</x:v>
-      </x:c>
-      <x:c r="B292" s="36"/>
-    </x:row>
-    <x:row r="293">
-      <x:c r="A293" s="33" t="str">
-        <x:v>execution_p_3145_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B293" s="36"/>
-    </x:row>
-    <x:row r="294">
-      <x:c r="A294" s="33" t="str">
-        <x:v>execution_p_3145_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B294" s="36"/>
-    </x:row>
-    <x:row r="295">
-      <x:c r="A295" s="33" t="str">
-        <x:v>execution_p_3145_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B295" s="36"/>
-    </x:row>
-    <x:row r="296">
-      <x:c r="A296" s="33" t="str">
-        <x:v>execution_p_3145_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B296" s="36"/>
-    </x:row>
-    <x:row r="297">
-      <x:c r="A297" s="33" t="str">
-        <x:v>execution_p_3145_completed_hours</x:v>
-      </x:c>
-      <x:c r="B297" s="36"/>
-    </x:row>
-    <x:row r="298">
-      <x:c r="A298" s="33" t="str">
-        <x:v>execution_p_3145_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B298" s="36"/>
-    </x:row>
-    <x:row r="299">
-      <x:c r="A299" s="33" t="str">
-        <x:v>execution_p_3145_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B299" s="36"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="A300" s="33" t="str">
-        <x:v>execution_p_3145_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B300" s="36"/>
-    </x:row>
-    <x:row r="301">
-      <x:c r="A301" s="33" t="str">
-        <x:v>execution_p_3145_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B301" s="36"/>
-    </x:row>
-    <x:row r="302">
-      <x:c r="A302" s="33" t="str">
-        <x:v>execution_p_3145_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B302" s="36"/>
-    </x:row>
-    <x:row r="303">
-      <x:c r="A303" s="33" t="str">
-        <x:v>execution_p_3145_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B303" s="36"/>
-    </x:row>
-    <x:row r="304">
-      <x:c r="A304" s="33" t="str">
-        <x:v>execution_p_3145_release_status</x:v>
-      </x:c>
-      <x:c r="B304" s="36"/>
-    </x:row>
-    <x:row r="305">
-      <x:c r="A305" s="33" t="str">
-        <x:v>execution_p_3122_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B305" s="36"/>
-    </x:row>
-    <x:row r="306">
-      <x:c r="A306" s="33" t="str">
-        <x:v>execution_p_3122_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B306" s="36"/>
-    </x:row>
-    <x:row r="307">
-      <x:c r="A307" s="33" t="str">
-        <x:v>execution_p_3122_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B307" s="36"/>
-    </x:row>
-    <x:row r="308">
-      <x:c r="A308" s="33" t="str">
-        <x:v>execution_p_3122_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B308" s="36"/>
-    </x:row>
-    <x:row r="309">
-      <x:c r="A309" s="33" t="str">
-        <x:v>execution_p_3122_completed_hours</x:v>
-      </x:c>
-      <x:c r="B309" s="36"/>
-    </x:row>
-    <x:row r="310">
-      <x:c r="A310" s="33" t="str">
-        <x:v>execution_p_3122_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B310" s="36"/>
-    </x:row>
-    <x:row r="311">
-      <x:c r="A311" s="33" t="str">
-        <x:v>execution_p_3122_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B311" s="36"/>
-    </x:row>
-    <x:row r="312">
-      <x:c r="A312" s="33" t="str">
-        <x:v>execution_p_3122_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B312" s="36"/>
-    </x:row>
-    <x:row r="313">
-      <x:c r="A313" s="33" t="str">
-        <x:v>execution_p_3122_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B313" s="36"/>
-    </x:row>
-    <x:row r="314">
-      <x:c r="A314" s="33" t="str">
-        <x:v>execution_p_3122_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B314" s="36"/>
-    </x:row>
-    <x:row r="315">
-      <x:c r="A315" s="33" t="str">
-        <x:v>execution_p_3122_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B315" s="36"/>
-    </x:row>
-    <x:row r="316">
-      <x:c r="A316" s="33" t="str">
-        <x:v>execution_p_3122_release_status</x:v>
-      </x:c>
-      <x:c r="B316" s="36"/>
-    </x:row>
-    <x:row r="317">
-      <x:c r="A317" s="33" t="str">
-        <x:v>execution_p_3152_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B317" s="36"/>
-    </x:row>
-    <x:row r="318">
-      <x:c r="A318" s="33" t="str">
-        <x:v>execution_p_3152_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B318" s="36"/>
-    </x:row>
-    <x:row r="319">
-      <x:c r="A319" s="33" t="str">
-        <x:v>execution_p_3152_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B319" s="36"/>
-    </x:row>
-    <x:row r="320">
-      <x:c r="A320" s="33" t="str">
-        <x:v>execution_p_3152_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B320" s="36"/>
-    </x:row>
-    <x:row r="321">
-      <x:c r="A321" s="33" t="str">
-        <x:v>execution_p_3152_completed_hours</x:v>
-      </x:c>
-      <x:c r="B321" s="36"/>
-    </x:row>
-    <x:row r="322">
-      <x:c r="A322" s="33" t="str">
-        <x:v>execution_p_3152_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B322" s="36"/>
-    </x:row>
-    <x:row r="323">
-      <x:c r="A323" s="33" t="str">
-        <x:v>execution_p_3152_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B323" s="36"/>
-    </x:row>
-    <x:row r="324">
-      <x:c r="A324" s="33" t="str">
-        <x:v>execution_p_3152_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B324" s="36"/>
-    </x:row>
-    <x:row r="325">
-      <x:c r="A325" s="33" t="str">
-        <x:v>execution_p_3152_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B325" s="36"/>
-    </x:row>
-    <x:row r="326">
-      <x:c r="A326" s="33" t="str">
-        <x:v>execution_p_3152_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B326" s="36"/>
-    </x:row>
-    <x:row r="327">
-      <x:c r="A327" s="33" t="str">
-        <x:v>execution_p_3152_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B327" s="36"/>
-    </x:row>
-    <x:row r="328">
-      <x:c r="A328" s="33" t="str">
-        <x:v>execution_p_3152_release_status</x:v>
-      </x:c>
-      <x:c r="B328" s="36"/>
-    </x:row>
-    <x:row r="329">
-      <x:c r="A329" s="33" t="str">
-        <x:v>execution_p_3138_customer_delivery_priority</x:v>
-      </x:c>
-      <x:c r="B329" s="36"/>
-    </x:row>
-    <x:row r="330">
-      <x:c r="A330" s="33" t="str">
-        <x:v>execution_p_3138_contract_gross_margin</x:v>
-      </x:c>
-      <x:c r="B330" s="36"/>
-    </x:row>
-    <x:row r="331">
-      <x:c r="A331" s="33" t="str">
-        <x:v>execution_p_3138_monthly_liquidated_damages_rate</x:v>
-      </x:c>
-      <x:c r="B331" s="36"/>
-    </x:row>
-    <x:row r="332">
-      <x:c r="A332" s="33" t="str">
-        <x:v>execution_p_3138_signed_backlog</x:v>
-      </x:c>
-      <x:c r="B332" s="36"/>
-    </x:row>
-    <x:row r="333">
-      <x:c r="A333" s="33" t="str">
-        <x:v>execution_p_3138_completed_hours</x:v>
-      </x:c>
-      <x:c r="B333" s="36"/>
-    </x:row>
-    <x:row r="334">
-      <x:c r="A334" s="33" t="str">
-        <x:v>execution_p_3138_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B334" s="36"/>
-    </x:row>
-    <x:row r="335">
-      <x:c r="A335" s="33" t="str">
-        <x:v>execution_p_3138_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B335" s="36"/>
-    </x:row>
-    <x:row r="336">
-      <x:c r="A336" s="33" t="str">
-        <x:v>execution_p_3138_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B336" s="36"/>
-    </x:row>
-    <x:row r="337">
-      <x:c r="A337" s="33" t="str">
-        <x:v>execution_p_3138_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B337" s="36"/>
-    </x:row>
-    <x:row r="338">
-      <x:c r="A338" s="33" t="str">
-        <x:v>execution_p_3138_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B338" s="36"/>
-    </x:row>
-    <x:row r="339">
-      <x:c r="A339" s="33" t="str">
-        <x:v>execution_p_3138_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B339" s="36"/>
-    </x:row>
-    <x:row r="340">
-      <x:c r="A340" s="33" t="str">
-        <x:v>execution_p_3138_release_status</x:v>
-      </x:c>
-      <x:c r="B340" s="36"/>
-    </x:row>
-    <x:row r="341">
-      <x:c r="A341" s="33" t="str">
-        <x:v>execution_portfolio_completed_revenue</x:v>
-      </x:c>
-      <x:c r="B341" s="36"/>
-    </x:row>
-    <x:row r="342">
-      <x:c r="A342" s="33" t="str">
-        <x:v>execution_portfolio_ending_deferred_revenue</x:v>
-      </x:c>
-      <x:c r="B342" s="36"/>
-    </x:row>
-    <x:row r="343">
-      <x:c r="A343" s="33" t="str">
-        <x:v>execution_portfolio_revenue_check_delta</x:v>
-      </x:c>
-      <x:c r="B343" s="36"/>
-    </x:row>
-    <x:row r="344">
-      <x:c r="A344" s="33" t="str">
-        <x:v>execution_portfolio_ending_deferred_hours</x:v>
-      </x:c>
-      <x:c r="B344" s="36"/>
-    </x:row>
-    <x:row r="345">
-      <x:c r="A345" s="33" t="str">
-        <x:v>execution_portfolio_completed_gross_profit</x:v>
-      </x:c>
-      <x:c r="B345" s="36"/>
-    </x:row>
-    <x:row r="346">
-      <x:c r="A346" s="33" t="str">
-        <x:v>execution_portfolio_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B346" s="36"/>
-    </x:row>
-    <x:row r="347">
-      <x:c r="A347" s="33" t="str">
-        <x:v>execution_portfolio_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B347" s="36"/>
-    </x:row>
-    <x:row r="348">
-      <x:c r="A348" s="33" t="str">
-        <x:v>execution_portfolio_highest_priority_deferred_project</x:v>
-      </x:c>
-      <x:c r="B348" s="36"/>
-    </x:row>
-    <x:row r="349">
-      <x:c r="A349" s="33" t="str">
-        <x:v>execution_portfolio_release_status</x:v>
-      </x:c>
-      <x:c r="B349" s="36"/>
-    </x:row>
-    <x:row r="350">
-      <x:c r="A350" s="33" t="str">
-        <x:v>release_bridge_probability_plan_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B350" s="36"/>
-    </x:row>
-    <x:row r="351">
-      <x:c r="A351" s="33" t="str">
-        <x:v>release_bridge_gross_commitment_gross_profit_after_remediation</x:v>
-      </x:c>
-      <x:c r="B351" s="36"/>
-    </x:row>
-    <x:row r="352">
-      <x:c r="A352" s="33" t="str">
-        <x:v>release_bridge_execution_net_gross_profit_after_damages</x:v>
-      </x:c>
-      <x:c r="B352" s="36"/>
-    </x:row>
-    <x:row r="353">
-      <x:c r="A353" s="33" t="str">
-        <x:v>release_bridge_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B353" s="36"/>
-    </x:row>
-    <x:row r="354">
-      <x:c r="A354" s="33" t="str">
-        <x:v>release_bridge_management_decision</x:v>
-      </x:c>
-      <x:c r="B354" s="36"/>
-    </x:row>
-    <x:row r="355">
-      <x:c r="A355" s="33" t="str">
-        <x:v>executive_recovery_probability_plan_gp_after_remediation</x:v>
-      </x:c>
-      <x:c r="B355" s="36"/>
-    </x:row>
-    <x:row r="356">
-      <x:c r="A356" s="33" t="str">
-        <x:v>executive_recovery_gross_commitment_gp_after_remediation</x:v>
-      </x:c>
-      <x:c r="B356" s="36"/>
-    </x:row>
-    <x:row r="357">
-      <x:c r="A357" s="33" t="str">
-        <x:v>executive_recovery_execution_net_gp_after_damages</x:v>
-      </x:c>
-      <x:c r="B357" s="36"/>
-    </x:row>
-    <x:row r="358">
-      <x:c r="A358" s="33" t="str">
-        <x:v>executive_recovery_probability_plan_variance</x:v>
-      </x:c>
-      <x:c r="B358" s="36"/>
-    </x:row>
-    <x:row r="359">
-      <x:c r="A359" s="33" t="str">
-        <x:v>executive_recovery_gross_commitment_shortfall</x:v>
-      </x:c>
-      <x:c r="B359" s="36"/>
-    </x:row>
-    <x:row r="360">
-      <x:c r="A360" s="33" t="str">
-        <x:v>executive_recovery_deferred_revenue_at_risk</x:v>
-      </x:c>
-      <x:c r="B360" s="36"/>
-    </x:row>
-    <x:row r="361">
-      <x:c r="A361" s="33" t="str">
-        <x:v>executive_recovery_deferred_gross_profit_at_risk</x:v>
-      </x:c>
-      <x:c r="B361" s="36"/>
-    </x:row>
-    <x:row r="362">
-      <x:c r="A362" s="33" t="str">
-        <x:v>executive_recovery_liquidated_damages</x:v>
-      </x:c>
-      <x:c r="B362" s="36"/>
-    </x:row>
-    <x:row r="363">
-      <x:c r="A363" s="33" t="str">
-        <x:v>executive_recovery_required_recovery</x:v>
-      </x:c>
-      <x:c r="B363" s="36"/>
-    </x:row>
-    <x:row r="364">
-      <x:c r="A364" s="33" t="str">
-        <x:v>executive_recovery_highest_priority_deferred_project</x:v>
-      </x:c>
-      <x:c r="B364" s="36"/>
-    </x:row>
-    <x:row r="365">
-      <x:c r="A365" s="33" t="str">
-        <x:v>executive_recovery_required_action</x:v>
-      </x:c>
-      <x:c r="B365" s="36"/>
-    </x:row>
-    <x:row r="366">
-      <x:c r="A366" s="33" t="str">
-        <x:v>executive_recovery_release_condition</x:v>
-      </x:c>
-      <x:c r="B366" s="36"/>
-    </x:row>
-    <x:row r="367">
-      <x:c r="A367" s="34" t="str">
-        <x:v>executive_recovery_decision</x:v>
-      </x:c>
-      <x:c r="B367" s="37"/>
-    </x:row>
-    <x:row r="370" ht="30" customHeight="1">
-      <x:c r="A370" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B370" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C370" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D370" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E370" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F370" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G370" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H370" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="371">
-      <x:c r="A371" s="40"/>
-      <x:c r="B371" s="40"/>
-      <x:c r="C371" s="40"/>
-      <x:c r="D371" s="40"/>
-      <x:c r="E371" s="40"/>
-      <x:c r="F371" s="40"/>
-      <x:c r="G371" s="40"/>
-      <x:c r="H371" s="40"/>
-    </x:row>
-    <x:row r="372">
-      <x:c r="A372" s="41"/>
-      <x:c r="B372" s="41"/>
-      <x:c r="C372" s="41"/>
-      <x:c r="D372" s="41"/>
-      <x:c r="E372" s="41"/>
-      <x:c r="F372" s="41"/>
-      <x:c r="G372" s="41"/>
-      <x:c r="H372" s="41"/>
-    </x:row>
-    <x:row r="373">
-      <x:c r="A373" s="41"/>
-      <x:c r="B373" s="41"/>
-      <x:c r="C373" s="41"/>
-      <x:c r="D373" s="41"/>
-      <x:c r="E373" s="41"/>
-      <x:c r="F373" s="41"/>
-      <x:c r="G373" s="41"/>
-      <x:c r="H373" s="41"/>
-    </x:row>
-    <x:row r="374">
-      <x:c r="A374" s="41"/>
-      <x:c r="B374" s="41"/>
-      <x:c r="C374" s="41"/>
-      <x:c r="D374" s="41"/>
-      <x:c r="E374" s="41"/>
-      <x:c r="F374" s="41"/>
-      <x:c r="G374" s="41"/>
-      <x:c r="H374" s="41"/>
-    </x:row>
-    <x:row r="375">
-      <x:c r="A375" s="41"/>
-      <x:c r="B375" s="41"/>
-      <x:c r="C375" s="41"/>
-      <x:c r="D375" s="41"/>
-      <x:c r="E375" s="41"/>
-      <x:c r="F375" s="41"/>
-      <x:c r="G375" s="41"/>
-      <x:c r="H375" s="41"/>
-    </x:row>
-    <x:row r="376">
-      <x:c r="A376" s="41"/>
-      <x:c r="B376" s="41"/>
-      <x:c r="C376" s="41"/>
-      <x:c r="D376" s="41"/>
-      <x:c r="E376" s="41"/>
-      <x:c r="F376" s="41"/>
-      <x:c r="G376" s="41"/>
-      <x:c r="H376" s="41"/>
-    </x:row>
-    <x:row r="377">
-      <x:c r="A377" s="41"/>
-      <x:c r="B377" s="41"/>
-      <x:c r="C377" s="41"/>
-      <x:c r="D377" s="41"/>
-      <x:c r="E377" s="41"/>
-      <x:c r="F377" s="41"/>
-      <x:c r="G377" s="41"/>
-      <x:c r="H377" s="41"/>
-    </x:row>
-    <x:row r="378">
-      <x:c r="A378" s="41"/>
-      <x:c r="B378" s="41"/>
-      <x:c r="C378" s="41"/>
-      <x:c r="D378" s="41"/>
-      <x:c r="E378" s="41"/>
-      <x:c r="F378" s="41"/>
-      <x:c r="G378" s="41"/>
-      <x:c r="H378" s="41"/>
-    </x:row>
-    <x:row r="379">
-      <x:c r="A379" s="41"/>
-      <x:c r="B379" s="41"/>
-      <x:c r="C379" s="41"/>
-      <x:c r="D379" s="41"/>
-      <x:c r="E379" s="41"/>
-      <x:c r="F379" s="41"/>
-      <x:c r="G379" s="41"/>
-      <x:c r="H379" s="41"/>
-    </x:row>
-    <x:row r="380">
-      <x:c r="A380" s="41"/>
-      <x:c r="B380" s="41"/>
-      <x:c r="C380" s="41"/>
-      <x:c r="D380" s="41"/>
-      <x:c r="E380" s="41"/>
-      <x:c r="F380" s="41"/>
-      <x:c r="G380" s="41"/>
-      <x:c r="H380" s="41"/>
-    </x:row>
-    <x:row r="381">
-      <x:c r="A381" s="41"/>
-      <x:c r="B381" s="41"/>
-      <x:c r="C381" s="41"/>
-      <x:c r="D381" s="41"/>
-      <x:c r="E381" s="41"/>
-      <x:c r="F381" s="41"/>
-      <x:c r="G381" s="41"/>
-      <x:c r="H381" s="41"/>
-    </x:row>
-    <x:row r="382">
-      <x:c r="A382" s="42"/>
-      <x:c r="B382" s="42"/>
-      <x:c r="C382" s="42"/>
-      <x:c r="D382" s="42"/>
-      <x:c r="E382" s="42"/>
-      <x:c r="F382" s="42"/>
-      <x:c r="G382" s="42"/>
-      <x:c r="H382" s="42"/>
+      <x:c r="A28" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B28" s="47"/>
+      <x:c r="C28" s="47"/>
+      <x:c r="D28" s="47"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+    <x:mergeCell ref="A15:K15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -12428,17 +8846,20 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Checks</x:v>
+        <x:v>FY27 backlog and capacity | controls and executive decision</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -12447,10 +8868,12 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
+        <x:v>One assertion per control; the model is releasable only when the calculations and decision conditions agree</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -12459,6 +8882,8 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
@@ -12484,7 +8909,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
+      <x:c r="A5" s="35" t="str">
         <x:v>Source population tie</x:v>
       </x:c>
       <x:c r="B5" s="35"/>
@@ -12495,75 +8920,156 @@
       <x:c r="G5" s="35"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Current-versus-prior version</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
-      <x:c r="C6" s="36"/>
-      <x:c r="D6" s="36"/>
-      <x:c r="E6" s="36"/>
-      <x:c r="F6" s="36"/>
-      <x:c r="G6" s="36"/>
+      <x:c r="A6" s="50" t="str">
+        <x:v>Backlog roll-forward</x:v>
+      </x:c>
+      <x:c r="B6" s="50"/>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="50"/>
+      <x:c r="E6" s="50"/>
+      <x:c r="F6" s="50"/>
+      <x:c r="G6" s="50"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>Period completeness</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
-      <x:c r="C7" s="36"/>
-      <x:c r="D7" s="36"/>
-      <x:c r="E7" s="36"/>
-      <x:c r="F7" s="36"/>
-      <x:c r="G7" s="36"/>
+      <x:c r="A7" s="50" t="str">
+        <x:v>Probability-plan burn</x:v>
+      </x:c>
+      <x:c r="B7" s="50"/>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="50"/>
+      <x:c r="E7" s="50"/>
+      <x:c r="F7" s="50"/>
+      <x:c r="G7" s="50"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>Scenario validity</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
-      <x:c r="C8" s="36"/>
-      <x:c r="D8" s="36"/>
-      <x:c r="E8" s="36"/>
-      <x:c r="F8" s="36"/>
-      <x:c r="G8" s="36"/>
+      <x:c r="A8" s="50" t="str">
+        <x:v>Gross-commitment burn</x:v>
+      </x:c>
+      <x:c r="B8" s="50"/>
+      <x:c r="C8" s="50"/>
+      <x:c r="D8" s="50"/>
+      <x:c r="E8" s="50"/>
+      <x:c r="F8" s="50"/>
+      <x:c r="G8" s="50"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Unit conversion</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
-      <x:c r="C9" s="36"/>
-      <x:c r="D9" s="36"/>
-      <x:c r="E9" s="36"/>
-      <x:c r="F9" s="36"/>
-      <x:c r="G9" s="36"/>
+      <x:c r="A9" s="50" t="str">
+        <x:v>Capacity sign convention</x:v>
+      </x:c>
+      <x:c r="B9" s="50"/>
+      <x:c r="C9" s="50"/>
+      <x:c r="D9" s="50"/>
+      <x:c r="E9" s="50"/>
+      <x:c r="F9" s="50"/>
+      <x:c r="G9" s="50"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>Roll-forward / bridge</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
-      <x:c r="C10" s="36"/>
-      <x:c r="D10" s="36"/>
-      <x:c r="E10" s="36"/>
-      <x:c r="F10" s="36"/>
-      <x:c r="G10" s="36"/>
+      <x:c r="A10" s="50" t="str">
+        <x:v>Remediation sequence</x:v>
+      </x:c>
+      <x:c r="B10" s="50"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="50"/>
+      <x:c r="E10" s="50"/>
+      <x:c r="F10" s="50"/>
+      <x:c r="G10" s="50"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="34" t="str">
+      <x:c r="A11" s="50" t="str">
+        <x:v>Project-to-month roll-forward</x:v>
+      </x:c>
+      <x:c r="B11" s="50"/>
+      <x:c r="C11" s="50"/>
+      <x:c r="D11" s="50"/>
+      <x:c r="E11" s="50"/>
+      <x:c r="F11" s="50"/>
+      <x:c r="G11" s="50"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="50" t="str">
+        <x:v>Revenue and gross-profit bridge</x:v>
+      </x:c>
+      <x:c r="B12" s="50"/>
+      <x:c r="C12" s="50"/>
+      <x:c r="D12" s="50"/>
+      <x:c r="E12" s="50"/>
+      <x:c r="F12" s="50"/>
+      <x:c r="G12" s="50"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="36" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B11" s="37"/>
-      <x:c r="C11" s="37"/>
-      <x:c r="D11" s="37"/>
-      <x:c r="E11" s="37"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
+      <x:c r="B13" s="36"/>
+      <x:c r="C13" s="36"/>
+      <x:c r="D13" s="36"/>
+      <x:c r="E13" s="36"/>
+      <x:c r="F13" s="36"/>
+      <x:c r="G13" s="36"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="48" t="str">
+        <x:v>EXECUTIVE RECOVERY DECISION</x:v>
+      </x:c>
+      <x:c r="B16" s="48"/>
+      <x:c r="C16" s="48"/>
+      <x:c r="D16" s="48"/>
+      <x:c r="E16" s="48"/>
+      <x:c r="F16" s="48"/>
+      <x:c r="G16" s="48"/>
+      <x:c r="H16" s="48"/>
+      <x:c r="I16" s="48"/>
+      <x:c r="J16" s="48"/>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
+        <x:v>Probability-plan GP</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="str">
+        <x:v>Gross-commitment GP</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="str">
+        <x:v>Executable GP after damages</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="str">
+        <x:v>Deferred revenue</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="str">
+        <x:v>Deferred gross profit</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="str">
+        <x:v>Damages</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str">
+        <x:v>Recovery required</x:v>
+      </x:c>
+      <x:c r="I17" s="16" t="str">
+        <x:v>Priority item</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="str">
+        <x:v>Release condition / owner action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="51"/>
+      <x:c r="B18" s="51"/>
+      <x:c r="C18" s="51"/>
+      <x:c r="D18" s="51"/>
+      <x:c r="E18" s="51"/>
+      <x:c r="F18" s="51"/>
+      <x:c r="G18" s="51"/>
+      <x:c r="H18" s="51"/>
+      <x:c r="I18" s="51"/>
+      <x:c r="J18" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A16:J16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/environment/seed/sources/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
+++ b/environment/seed/sources/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="R90adb9c2d0964e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="R6176971d7bd54b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Authority" sheetId="3" r:id="R68d9e667df264edb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="4" r:id="Rea1d39ada1cd4a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="5" r:id="Rb682917fa0e74c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="6" r:id="R6f700491523f4ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Execution" sheetId="7" r:id="R950509ee15ef4959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R327d31c450c44878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Authority" sheetId="3" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="4" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="5" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="6" r:id="rId10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Execution" sheetId="7" r:id="rId11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="rId12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,7 +63,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,21 +87,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2EFE6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF5E8C8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF8F5EF"/>
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -161,19 +151,11 @@
         <x:color rgb="FFD8D0C6"/>
       </x:top>
     </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD8D0C6"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD8D0C6"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -239,46 +221,43 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -289,7 +268,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{4F0CFD4D-9CDB-4176-9E2A-5A351BEAA3FF}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{288C501C-B978-A961-E0AF-1C0C5B57B34D}"/>
 </xltc:personList>
 </file>
 
@@ -504,7 +483,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Contract Backlog</x:v>
+        <x:v>FY27 backlog delivery plan | Contract Backlog</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -520,7 +499,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
+        <x:v>REFERENCE SCHEDULE • source and date retained • do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -599,7 +578,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J5" s="22" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K5" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -633,7 +612,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J6" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K6" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -667,7 +646,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J7" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K7" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -701,7 +680,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J8" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K8" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -735,7 +714,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J9" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K9" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -769,7 +748,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J10" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K10" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -803,7 +782,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J11" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K11" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -837,7 +816,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J12" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K12" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -871,7 +850,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J13" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K13" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -905,7 +884,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J14" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K14" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -939,7 +918,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J15" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K15" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -973,7 +952,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J16" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K16" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1007,7 +986,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J17" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K17" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1041,7 +1020,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J18" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K18" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1075,7 +1054,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J19" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K19" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1109,7 +1088,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J20" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K20" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1143,7 +1122,7 @@
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K21" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1177,7 +1156,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J22" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K22" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1211,7 +1190,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J23" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K23" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1245,7 +1224,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J24" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1279,7 +1258,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J25" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K25" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1313,7 +1292,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J26" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K26" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1347,7 +1326,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J27" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K27" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1381,7 +1360,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J28" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K28" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1415,7 +1394,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J29" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K29" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1449,7 +1428,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J30" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K30" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1483,7 +1462,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J31" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K31" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1517,7 +1496,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J32" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K32" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1551,7 +1530,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J33" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K33" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1585,7 +1564,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J34" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K34" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1619,7 +1598,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J35" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K35" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1653,7 +1632,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J36" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K36" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1687,7 +1666,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J37" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K37" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1721,7 +1700,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J38" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K38" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1755,7 +1734,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J39" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K39" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1789,7 +1768,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J40" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K40" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1823,7 +1802,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J41" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K41" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1857,7 +1836,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J42" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K42" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1891,7 +1870,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J43" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K43" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1925,7 +1904,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J44" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K44" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1959,7 +1938,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J45" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K45" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1993,7 +1972,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J46" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K46" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2027,7 +2006,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J47" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K47" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2061,7 +2040,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J48" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K48" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2095,7 +2074,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J49" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K49" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2129,7 +2108,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J50" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K50" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2163,7 +2142,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J51" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K51" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2197,7 +2176,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J52" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K52" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2231,7 +2210,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J53" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K53" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2265,7 +2244,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J54" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K54" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2299,7 +2278,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J55" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K55" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2333,7 +2312,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J56" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K56" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2367,7 +2346,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J57" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K57" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2401,7 +2380,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J58" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K58" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2435,7 +2414,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J59" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K59" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2469,7 +2448,7 @@
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J60" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K60" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2503,7 +2482,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J61" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K61" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2537,7 +2516,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J62" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K62" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2571,7 +2550,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J63" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K63" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2605,7 +2584,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J64" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K64" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2639,7 +2618,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J65" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K65" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2673,7 +2652,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J66" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K66" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2707,7 +2686,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J67" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K67" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2741,7 +2720,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J68" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K68" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2775,7 +2754,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J69" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K69" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2809,7 +2788,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J70" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K70" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2843,7 +2822,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J71" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K71" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2877,7 +2856,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J72" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K72" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2911,7 +2890,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J73" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K73" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2945,7 +2924,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J74" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K74" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -2979,7 +2958,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J75" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K75" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3013,7 +2992,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J76" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K76" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3047,7 +3026,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J77" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K77" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3081,7 +3060,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J78" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K78" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3115,7 +3094,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J79" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K79" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3149,7 +3128,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J80" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K80" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3183,7 +3162,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J81" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K81" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3217,7 +3196,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J82" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K82" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3251,7 +3230,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J83" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K83" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3285,7 +3264,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J84" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K84" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3319,7 +3298,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J85" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K85" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3353,7 +3332,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J86" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K86" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3387,7 +3366,7 @@
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J87" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K87" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3421,7 +3400,7 @@
         <x:v>classification</x:v>
       </x:c>
       <x:c r="J88" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K88" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3455,7 +3434,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J89" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K89" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3489,7 +3468,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J90" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K90" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3523,7 +3502,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J91" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K91" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3557,7 +3536,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J92" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
       </x:c>
       <x:c r="K92" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3565,38 +3544,480 @@
       <x:c r="L92" s="23" t="str"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="24" t="str">
+      <x:c r="A93" s="23" t="str">
         <x:v>035-SRC0113</x:v>
       </x:c>
-      <x:c r="B93" s="24" t="str">
+      <x:c r="B93" s="23" t="str">
         <x:v>Project burn curve</x:v>
       </x:c>
-      <x:c r="C93" s="24" t="str">
+      <x:c r="C93" s="23" t="str">
         <x:v>P-3152</x:v>
       </x:c>
-      <x:c r="D93" s="24" t="str">
+      <x:c r="D93" s="23" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="E93" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F93" s="24" t="str">
+      <x:c r="E93" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F93" s="23" t="str">
         <x:v>Monthly burn share</x:v>
       </x:c>
-      <x:c r="G93" s="27" t="n">
+      <x:c r="G93" s="26" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="H93" s="24" t="str"/>
-      <x:c r="I93" s="24" t="str">
-        <x:v>decimal ratio</x:v>
-      </x:c>
-      <x:c r="J93" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K93" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L93" s="24" t="str"/>
+      <x:c r="H93" s="23" t="str"/>
+      <x:c r="I93" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J93" s="23" t="str">
+        <x:v>CRM backlog service renewals + forecast history_6.30.csv</x:v>
+      </x:c>
+      <x:c r="K93" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L93" s="23" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="23" t="str">
+        <x:v>035-SRC0198</x:v>
+      </x:c>
+      <x:c r="B94" s="23" t="str">
+        <x:v>Signed contract backlog</x:v>
+      </x:c>
+      <x:c r="C94" s="23" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D94" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E94" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F94" s="23" t="str">
+        <x:v>Remaining transaction price</x:v>
+      </x:c>
+      <x:c r="G94" s="26" t="n">
+        <x:v>8652000</x:v>
+      </x:c>
+      <x:c r="H94" s="23" t="str"/>
+      <x:c r="I94" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J94" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K94" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L94" s="23" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="23" t="str">
+        <x:v>035-SRC0199</x:v>
+      </x:c>
+      <x:c r="B95" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C95" s="23" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D95" s="23" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="E95" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F95" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G95" s="26" t="n">
+        <x:v>0.02666666666666667</x:v>
+      </x:c>
+      <x:c r="H95" s="23" t="str"/>
+      <x:c r="I95" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J95" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K95" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L95" s="23" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="23" t="str">
+        <x:v>035-SRC0200</x:v>
+      </x:c>
+      <x:c r="B96" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C96" s="23" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D96" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E96" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F96" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G96" s="26" t="n">
+        <x:v>0.12115384615384617</x:v>
+      </x:c>
+      <x:c r="H96" s="23" t="str"/>
+      <x:c r="I96" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J96" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K96" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L96" s="23" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="23" t="str">
+        <x:v>035-SRC0202</x:v>
+      </x:c>
+      <x:c r="B97" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C97" s="23" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="D97" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E97" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F97" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G97" s="26" t="n">
+        <x:v>0.0787878787878788</x:v>
+      </x:c>
+      <x:c r="H97" s="23" t="str"/>
+      <x:c r="I97" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J97" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K97" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L97" s="23" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="23" t="str">
+        <x:v>035-SRC0203</x:v>
+      </x:c>
+      <x:c r="B98" s="23" t="str">
+        <x:v>Signed contract backlog</x:v>
+      </x:c>
+      <x:c r="C98" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D98" s="23" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E98" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F98" s="23" t="str">
+        <x:v>Remaining transaction price</x:v>
+      </x:c>
+      <x:c r="G98" s="26" t="n">
+        <x:v>5880000</x:v>
+      </x:c>
+      <x:c r="H98" s="23" t="str"/>
+      <x:c r="I98" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J98" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K98" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L98" s="23" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="23" t="str">
+        <x:v>035-SRC0204</x:v>
+      </x:c>
+      <x:c r="B99" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C99" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D99" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E99" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F99" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G99" s="26" t="n">
+        <x:v>0.04577777777777778</x:v>
+      </x:c>
+      <x:c r="H99" s="23" t="str"/>
+      <x:c r="I99" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J99" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K99" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L99" s="23" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="23" t="str">
+        <x:v>035-SRC0205</x:v>
+      </x:c>
+      <x:c r="B100" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C100" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D100" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E100" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F100" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G100" s="26" t="n">
+        <x:v>0.20800000000000002</x:v>
+      </x:c>
+      <x:c r="H100" s="23" t="str"/>
+      <x:c r="I100" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J100" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K100" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L100" s="23" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="23" t="str">
+        <x:v>035-SRC0206</x:v>
+      </x:c>
+      <x:c r="B101" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C101" s="23" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="D101" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E101" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F101" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G101" s="26" t="n">
+        <x:v>0.0375</x:v>
+      </x:c>
+      <x:c r="H101" s="23" t="str"/>
+      <x:c r="I101" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J101" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K101" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L101" s="23" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="23" t="str">
+        <x:v>035-SRC0207</x:v>
+      </x:c>
+      <x:c r="B102" s="23" t="str">
+        <x:v>Signed contract backlog</x:v>
+      </x:c>
+      <x:c r="C102" s="23" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="D102" s="23" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E102" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F102" s="23" t="str">
+        <x:v>Remaining transaction price</x:v>
+      </x:c>
+      <x:c r="G102" s="26" t="n">
+        <x:v>7416000</x:v>
+      </x:c>
+      <x:c r="H102" s="23" t="str"/>
+      <x:c r="I102" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J102" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K102" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L102" s="23" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="23" t="str">
+        <x:v>035-SRC0208</x:v>
+      </x:c>
+      <x:c r="B103" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C103" s="23" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="D103" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E103" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F103" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G103" s="26" t="n">
+        <x:v>0.09904761904761905</x:v>
+      </x:c>
+      <x:c r="H103" s="23" t="str"/>
+      <x:c r="I103" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J103" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K103" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L103" s="23" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="23" t="str">
+        <x:v>035-SRC0209</x:v>
+      </x:c>
+      <x:c r="B104" s="23" t="str">
+        <x:v>Signed contract backlog</x:v>
+      </x:c>
+      <x:c r="C104" s="23" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="D104" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E104" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F104" s="23" t="str">
+        <x:v>Revenue per productive hour</x:v>
+      </x:c>
+      <x:c r="G104" s="26" t="n">
+        <x:v>131.25</x:v>
+      </x:c>
+      <x:c r="H104" s="23" t="str"/>
+      <x:c r="I104" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J104" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K104" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L104" s="23" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="23" t="str">
+        <x:v>035-SRC0210</x:v>
+      </x:c>
+      <x:c r="B105" s="23" t="str">
+        <x:v>Project burn curve</x:v>
+      </x:c>
+      <x:c r="C105" s="23" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="D105" s="23" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E105" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F105" s="23" t="str">
+        <x:v>Monthly burn share</x:v>
+      </x:c>
+      <x:c r="G105" s="26" t="n">
+        <x:v>0.27466666666666667</x:v>
+      </x:c>
+      <x:c r="H105" s="23" t="str"/>
+      <x:c r="I105" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J105" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K105" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L105" s="23" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="24" t="str">
+        <x:v>035-SRC0212</x:v>
+      </x:c>
+      <x:c r="B106" s="24" t="str">
+        <x:v>Signed contract backlog</x:v>
+      </x:c>
+      <x:c r="C106" s="24" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="D106" s="24" t="str">
+        <x:v>2026-05 working copy</x:v>
+      </x:c>
+      <x:c r="E106" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F106" s="24" t="str">
+        <x:v>Revenue per productive hour</x:v>
+      </x:c>
+      <x:c r="G106" s="27" t="n">
+        <x:v>136.5</x:v>
+      </x:c>
+      <x:c r="H106" s="24" t="str"/>
+      <x:c r="I106" s="24" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J106" s="24" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K106" s="30" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L106" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3627,7 +4048,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Capacity Inputs</x:v>
+        <x:v>FY27 backlog delivery plan | Capacity Inputs</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3643,7 +4064,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
+        <x:v>REFERENCE SCHEDULE • source and date retained • do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3722,7 +4143,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J5" s="22" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K5" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -3756,7 +4177,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J6" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K6" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3790,7 +4211,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J7" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K7" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3824,7 +4245,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J8" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K8" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3858,7 +4279,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J9" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K9" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3892,7 +4313,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J10" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K10" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3926,7 +4347,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J11" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K11" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3960,7 +4381,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J12" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K12" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3994,7 +4415,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J13" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K13" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4028,7 +4449,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J14" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K14" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4062,7 +4483,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J15" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K15" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4096,7 +4517,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J16" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K16" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4130,7 +4551,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J17" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K17" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4164,7 +4585,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J18" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K18" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4198,7 +4619,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J19" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K19" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4232,7 +4653,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J20" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K20" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4266,7 +4687,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K21" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4300,7 +4721,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J22" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K22" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4334,7 +4755,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J23" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K23" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4368,7 +4789,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J24" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4402,7 +4823,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J25" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K25" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4436,7 +4857,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J26" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K26" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4470,7 +4891,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J27" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K27" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4504,7 +4925,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J28" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K28" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4538,7 +4959,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J29" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K29" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4572,7 +4993,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J30" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K30" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4606,7 +5027,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J31" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K31" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4640,7 +5061,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J32" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K32" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4674,7 +5095,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J33" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K33" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4708,7 +5129,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J34" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K34" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4742,7 +5163,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J35" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K35" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4776,7 +5197,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J36" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K36" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4810,7 +5231,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J37" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K37" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4844,7 +5265,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J38" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K38" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4878,7 +5299,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J39" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K39" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4912,7 +5333,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J40" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K40" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4946,7 +5367,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J41" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K41" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4980,7 +5401,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J42" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K42" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5014,7 +5435,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J43" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K43" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5048,7 +5469,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J44" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K44" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5082,7 +5503,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J45" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K45" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5116,7 +5537,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J46" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K46" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5150,7 +5571,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J47" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K47" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5184,7 +5605,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J48" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K48" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5218,7 +5639,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J49" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K49" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5252,7 +5673,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J50" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K50" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5286,7 +5707,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J51" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K51" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5320,7 +5741,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J52" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K52" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5354,7 +5775,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J53" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K53" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5388,7 +5809,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J54" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K54" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5422,7 +5843,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J55" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K55" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5456,7 +5877,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J56" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K56" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5490,7 +5911,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J57" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K57" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5524,7 +5945,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J58" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K58" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5558,7 +5979,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J59" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K59" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5592,7 +6013,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J60" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K60" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5626,7 +6047,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J61" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K61" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5660,7 +6081,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J62" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K62" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5694,7 +6115,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J63" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K63" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5728,7 +6149,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J64" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K64" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5762,7 +6183,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J65" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K65" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5796,7 +6217,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J66" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K66" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5830,7 +6251,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J67" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K67" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5864,7 +6285,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J68" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K68" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5898,7 +6319,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J69" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K69" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5932,7 +6353,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J70" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K70" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -5966,7 +6387,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J71" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K71" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6000,7 +6421,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J72" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K72" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6034,7 +6455,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J73" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K73" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6068,7 +6489,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J74" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K74" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6102,7 +6523,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J75" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K75" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6136,7 +6557,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J76" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K76" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6170,7 +6591,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J77" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K77" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6204,7 +6625,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J78" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K78" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6238,7 +6659,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J79" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K79" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6272,7 +6693,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J80" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K80" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6306,7 +6727,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J81" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K81" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6340,7 +6761,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J82" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K82" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6374,7 +6795,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J83" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K83" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6408,7 +6829,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J84" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K84" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6442,7 +6863,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J85" s="23" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K85" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6476,7 +6897,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J86" s="23" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K86" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6510,7 +6931,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J87" s="23" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K87" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6518,38 +6939,72 @@
       <x:c r="L87" s="23" t="str"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="24" t="str">
+      <x:c r="A88" s="23" t="str">
         <x:v>035-SRC0197</x:v>
       </x:c>
-      <x:c r="B88" s="24" t="str">
+      <x:c r="B88" s="23" t="str">
         <x:v>Capacity remediation</x:v>
       </x:c>
-      <x:c r="C88" s="24" t="str">
+      <x:c r="C88" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
-      <x:c r="D88" s="24" t="str">
+      <x:c r="D88" s="23" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="E88" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F88" s="24" t="str">
+      <x:c r="E88" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F88" s="23" t="str">
         <x:v>Contingent subcontract cost</x:v>
       </x:c>
-      <x:c r="G88" s="27" t="n">
+      <x:c r="G88" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H88" s="24" t="str"/>
-      <x:c r="I88" s="24" t="str">
+      <x:c r="H88" s="23" t="str"/>
+      <x:c r="I88" s="23" t="str">
         <x:v>USD per hour</x:v>
       </x:c>
-      <x:c r="J88" s="24" t="str">
-        <x:v>Executed contingent labor framework</x:v>
-      </x:c>
-      <x:c r="K88" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L88" s="24" t="str"/>
+      <x:c r="J88" s="23" t="str">
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
+      </x:c>
+      <x:c r="K88" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L88" s="23" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="24" t="str">
+        <x:v>035-SRC0213</x:v>
+      </x:c>
+      <x:c r="B89" s="24" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C89" s="24" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D89" s="24" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="E89" s="24" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F89" s="24" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G89" s="27" t="n">
+        <x:v>32445</x:v>
+      </x:c>
+      <x:c r="H89" s="24" t="str"/>
+      <x:c r="I89" s="24" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J89" s="24" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K89" s="30" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L89" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6580,7 +7035,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Execution Authority</x:v>
+        <x:v>FY27 backlog delivery plan | Execution Authority</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -6596,7 +7051,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
+        <x:v>REFERENCE SCHEDULE • source and date retained • do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -6668,14 +7123,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="22" t="str"/>
       <x:c r="I5" s="22" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J5" s="22" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K5" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -6709,7 +7164,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J6" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K6" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6743,7 +7198,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J7" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K7" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6770,14 +7225,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G8" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H8" s="23" t="str"/>
       <x:c r="I8" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J8" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K8" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6811,7 +7266,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J9" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K9" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6845,7 +7300,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J10" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K10" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6879,7 +7334,7 @@
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J11" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K11" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6913,7 +7368,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J12" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K12" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6947,7 +7402,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J13" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K13" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -6974,14 +7429,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G14" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="23" t="str"/>
       <x:c r="I14" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J14" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K14" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7015,7 +7470,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J15" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K15" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7049,7 +7504,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J16" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K16" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7076,14 +7531,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G17" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="23" t="str"/>
       <x:c r="I17" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J17" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K17" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7117,7 +7572,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J18" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K18" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7151,7 +7606,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J19" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K19" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7178,14 +7633,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G20" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="23" t="str"/>
       <x:c r="I20" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J20" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K20" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7219,7 +7674,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K21" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7253,7 +7708,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J22" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K22" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7280,14 +7735,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G23" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H23" s="23" t="str"/>
       <x:c r="I23" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J23" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K23" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7321,7 +7776,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J24" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7355,7 +7810,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J25" s="23" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K25" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7382,14 +7837,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="G26" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H26" s="23" t="str"/>
       <x:c r="I26" s="23" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="J26" s="23" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K26" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7423,7 +7878,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J27" s="23" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="K27" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -7431,38 +7886,106 @@
       <x:c r="L27" s="23" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="24" t="str">
+      <x:c r="A28" s="23" t="str">
         <x:v>035-SRC0110</x:v>
       </x:c>
-      <x:c r="B28" s="24" t="str">
+      <x:c r="B28" s="23" t="str">
         <x:v>Execution authority</x:v>
       </x:c>
-      <x:c r="C28" s="24" t="str">
+      <x:c r="C28" s="23" t="str">
         <x:v>P-3152</x:v>
       </x:c>
-      <x:c r="D28" s="24" t="str">
+      <x:c r="D28" s="23" t="str">
         <x:v>FY27</x:v>
       </x:c>
-      <x:c r="E28" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F28" s="24" t="str">
+      <x:c r="E28" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F28" s="23" t="str">
         <x:v>Monthly liquidated damages rate</x:v>
       </x:c>
-      <x:c r="G28" s="27" t="n">
+      <x:c r="G28" s="26" t="n">
         <x:v>0.014</x:v>
       </x:c>
-      <x:c r="H28" s="24" t="str"/>
-      <x:c r="I28" s="24" t="str">
-        <x:v>decimal ratio</x:v>
-      </x:c>
-      <x:c r="J28" s="24" t="str">
-        <x:v>Executed contract terms</x:v>
-      </x:c>
-      <x:c r="K28" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L28" s="24" t="str"/>
+      <x:c r="H28" s="23" t="str"/>
+      <x:c r="I28" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J28" s="23" t="str">
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
+      </x:c>
+      <x:c r="K28" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L28" s="23" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="23" t="str">
+        <x:v>035-SRC0201</x:v>
+      </x:c>
+      <x:c r="B29" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E29" s="23" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F29" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G29" s="26" t="n">
+        <x:v>4.12</x:v>
+      </x:c>
+      <x:c r="H29" s="23" t="str"/>
+      <x:c r="I29" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J29" s="23" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K29" s="29" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L29" s="23" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="24" t="str">
+        <x:v>035-SRC0211</x:v>
+      </x:c>
+      <x:c r="B30" s="24" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C30" s="24" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="D30" s="24" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E30" s="24" t="str">
+        <x:v>Management stretch</x:v>
+      </x:c>
+      <x:c r="F30" s="24" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G30" s="27" t="n">
+        <x:v>0.01144</x:v>
+      </x:c>
+      <x:c r="H30" s="24" t="str"/>
+      <x:c r="I30" s="24" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J30" s="24" t="str">
+        <x:v>FY27 planning assumptions - v4 branch draft.xlsx</x:v>
+      </x:c>
+      <x:c r="K30" s="30" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="L30" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7478,18 +8001,18 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>FY27 backlog burn | planning cases</x:v>
+        <x:v>FY27 backlog delivery | working model</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -7501,7 +8024,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build from the controlled source schedules; keep probability plan, signed commitment, and pipeline distinct</x:v>
+        <x:v>Complete the monthly analysis and retain formula and source traceability</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -7513,223 +8036,173 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Case</x:v>
+        <x:v>Month</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Signed backlog</x:v>
+        <x:v>Planning basis</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>FY27 revenue</x:v>
+        <x:v>Contract value</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Required hours</x:v>
+        <x:v>Revenue schedule</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>First constrained month</x:v>
+        <x:v>Productive hours</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>Unresolved hours</x:v>
+        <x:v>Gross profit</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>Remediation cost</x:v>
+        <x:v>Units</x:v>
       </x:c>
       <x:c r="H4" s="17" t="str">
-        <x:v>Release conclusion</x:v>
+        <x:v>Source / check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="35" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
-      <x:c r="C5" s="35"/>
-      <x:c r="D5" s="35"/>
-      <x:c r="E5" s="35"/>
-      <x:c r="F5" s="35"/>
-      <x:c r="G5" s="35"/>
-      <x:c r="H5" s="35"/>
+      <x:c r="A5" s="39" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B5" s="39"/>
+      <x:c r="C5" s="39"/>
+      <x:c r="D5" s="39"/>
+      <x:c r="E5" s="39"/>
+      <x:c r="F5" s="39"/>
+      <x:c r="G5" s="39"/>
+      <x:c r="H5" s="39"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="36" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
-      <x:c r="C6" s="36"/>
-      <x:c r="D6" s="36"/>
-      <x:c r="E6" s="36"/>
-      <x:c r="F6" s="36"/>
-      <x:c r="G6" s="36"/>
-      <x:c r="H6" s="36"/>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="15" t="str">
-        <x:v>Month</x:v>
-      </x:c>
-      <x:c r="B9" s="16" t="str">
-        <x:v>Probability-plan revenue</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="str">
-        <x:v>Gross-commitment revenue</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="str">
-        <x:v>Revenue variance</x:v>
-      </x:c>
-      <x:c r="E9" s="16" t="str">
-        <x:v>Probability-plan hours</x:v>
-      </x:c>
-      <x:c r="F9" s="16" t="str">
-        <x:v>Gross-commitment hours</x:v>
-      </x:c>
-      <x:c r="G9" s="16" t="str">
-        <x:v>Source / version</x:v>
-      </x:c>
-      <x:c r="H9" s="17" t="str">
-        <x:v>Control</x:v>
-      </x:c>
+      <x:c r="A6" s="40" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
+      <x:c r="G6" s="40"/>
+      <x:c r="H6" s="40"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="40" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="40" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
+      <x:c r="G8" s="40"/>
+      <x:c r="H8" s="40"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="40" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="45" t="str">
-        <x:v>2026-07</x:v>
-      </x:c>
-      <x:c r="B10" s="45"/>
-      <x:c r="C10" s="45"/>
-      <x:c r="D10" s="45"/>
-      <x:c r="E10" s="45"/>
-      <x:c r="F10" s="45"/>
-      <x:c r="G10" s="45"/>
-      <x:c r="H10" s="45"/>
+      <x:c r="A10" s="40" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
+      <x:c r="G10" s="40"/>
+      <x:c r="H10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="46" t="str">
-        <x:v>2026-08</x:v>
-      </x:c>
-      <x:c r="B11" s="46"/>
-      <x:c r="C11" s="46"/>
-      <x:c r="D11" s="46"/>
-      <x:c r="E11" s="46"/>
-      <x:c r="F11" s="46"/>
-      <x:c r="G11" s="46"/>
-      <x:c r="H11" s="46"/>
+      <x:c r="A11" s="40" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="46" t="str">
-        <x:v>2026-09</x:v>
-      </x:c>
-      <x:c r="B12" s="46"/>
-      <x:c r="C12" s="46"/>
-      <x:c r="D12" s="46"/>
-      <x:c r="E12" s="46"/>
-      <x:c r="F12" s="46"/>
-      <x:c r="G12" s="46"/>
-      <x:c r="H12" s="46"/>
+      <x:c r="A12" s="40" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B12" s="40"/>
+      <x:c r="C12" s="40"/>
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="40"/>
+      <x:c r="F12" s="40"/>
+      <x:c r="G12" s="40"/>
+      <x:c r="H12" s="40"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="46" t="str">
-        <x:v>2026-10</x:v>
-      </x:c>
-      <x:c r="B13" s="46"/>
-      <x:c r="C13" s="46"/>
-      <x:c r="D13" s="46"/>
-      <x:c r="E13" s="46"/>
-      <x:c r="F13" s="46"/>
-      <x:c r="G13" s="46"/>
-      <x:c r="H13" s="46"/>
+      <x:c r="A13" s="40" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B13" s="40"/>
+      <x:c r="C13" s="40"/>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="46" t="str">
-        <x:v>2026-11</x:v>
-      </x:c>
-      <x:c r="B14" s="46"/>
-      <x:c r="C14" s="46"/>
-      <x:c r="D14" s="46"/>
-      <x:c r="E14" s="46"/>
-      <x:c r="F14" s="46"/>
-      <x:c r="G14" s="46"/>
-      <x:c r="H14" s="46"/>
+      <x:c r="A14" s="40" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B14" s="40"/>
+      <x:c r="C14" s="40"/>
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="40"/>
+      <x:c r="F14" s="40"/>
+      <x:c r="G14" s="40"/>
+      <x:c r="H14" s="40"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="46" t="str">
-        <x:v>2026-12</x:v>
-      </x:c>
-      <x:c r="B15" s="46"/>
-      <x:c r="C15" s="46"/>
-      <x:c r="D15" s="46"/>
-      <x:c r="E15" s="46"/>
-      <x:c r="F15" s="46"/>
-      <x:c r="G15" s="46"/>
-      <x:c r="H15" s="46"/>
+      <x:c r="A15" s="40" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B15" s="40"/>
+      <x:c r="C15" s="40"/>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="46" t="str">
-        <x:v>2027-01</x:v>
-      </x:c>
-      <x:c r="B16" s="46"/>
-      <x:c r="C16" s="46"/>
-      <x:c r="D16" s="46"/>
-      <x:c r="E16" s="46"/>
-      <x:c r="F16" s="46"/>
-      <x:c r="G16" s="46"/>
-      <x:c r="H16" s="46"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="46" t="str">
-        <x:v>2027-02</x:v>
-      </x:c>
-      <x:c r="B17" s="46"/>
-      <x:c r="C17" s="46"/>
-      <x:c r="D17" s="46"/>
-      <x:c r="E17" s="46"/>
-      <x:c r="F17" s="46"/>
-      <x:c r="G17" s="46"/>
-      <x:c r="H17" s="46"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="46" t="str">
-        <x:v>2027-03</x:v>
-      </x:c>
-      <x:c r="B18" s="46"/>
-      <x:c r="C18" s="46"/>
-      <x:c r="D18" s="46"/>
-      <x:c r="E18" s="46"/>
-      <x:c r="F18" s="46"/>
-      <x:c r="G18" s="46"/>
-      <x:c r="H18" s="46"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="46" t="str">
-        <x:v>2027-04</x:v>
-      </x:c>
-      <x:c r="B19" s="46"/>
-      <x:c r="C19" s="46"/>
-      <x:c r="D19" s="46"/>
-      <x:c r="E19" s="46"/>
-      <x:c r="F19" s="46"/>
-      <x:c r="G19" s="46"/>
-      <x:c r="H19" s="46"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="46" t="str">
-        <x:v>2027-05</x:v>
-      </x:c>
-      <x:c r="B20" s="46"/>
-      <x:c r="C20" s="46"/>
-      <x:c r="D20" s="46"/>
-      <x:c r="E20" s="46"/>
-      <x:c r="F20" s="46"/>
-      <x:c r="G20" s="46"/>
-      <x:c r="H20" s="46"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="47" t="str">
+      <x:c r="A16" s="41" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="B21" s="47"/>
-      <x:c r="C21" s="47"/>
-      <x:c r="D21" s="47"/>
-      <x:c r="E21" s="47"/>
-      <x:c r="F21" s="47"/>
-      <x:c r="G21" s="47"/>
-      <x:c r="H21" s="47"/>
+      <x:c r="B16" s="41"/>
+      <x:c r="C16" s="41"/>
+      <x:c r="D16" s="41"/>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16" s="41"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7745,19 +8218,18 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>FY27 labor capacity | approved availability</x:v>
+        <x:v>FY27 labor capacity | working model</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -7766,11 +8238,10 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Reconcile recurring capacity and keep ordinary availability separate from emergency response</x:v>
+        <x:v>Complete the monthly availability analysis from the reference schedules</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -7779,197 +8250,181 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
-      <x:c r="I2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
         <x:v>Month</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Internal hours</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>Permitted overtime</x:v>
+        <x:v>Overtime hours</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Planned subcontractable</x:v>
+        <x:v>Subcontract hours</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>Base available hours</x:v>
+        <x:v>Available hours</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>Emergency OT capacity</x:v>
+        <x:v>Incremental cost</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>Contingent surge capacity</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>Remediated available hours</x:v>
-      </x:c>
-      <x:c r="I4" s="17" t="str">
-        <x:v>Source / authority</x:v>
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Source / check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="45" t="str">
+      <x:c r="A5" s="39" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="B5" s="45"/>
-      <x:c r="C5" s="45"/>
-      <x:c r="D5" s="45"/>
-      <x:c r="E5" s="45"/>
-      <x:c r="F5" s="45"/>
-      <x:c r="G5" s="45"/>
-      <x:c r="H5" s="45"/>
-      <x:c r="I5" s="45"/>
+      <x:c r="B5" s="39"/>
+      <x:c r="C5" s="39"/>
+      <x:c r="D5" s="39"/>
+      <x:c r="E5" s="39"/>
+      <x:c r="F5" s="39"/>
+      <x:c r="G5" s="39"/>
+      <x:c r="H5" s="39"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="40" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="B6" s="46"/>
-      <x:c r="C6" s="46"/>
-      <x:c r="D6" s="46"/>
-      <x:c r="E6" s="46"/>
-      <x:c r="F6" s="46"/>
-      <x:c r="G6" s="46"/>
-      <x:c r="H6" s="46"/>
-      <x:c r="I6" s="46"/>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
+      <x:c r="G6" s="40"/>
+      <x:c r="H6" s="40"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="40" t="str">
         <x:v>2026-09</x:v>
       </x:c>
-      <x:c r="B7" s="46"/>
-      <x:c r="C7" s="46"/>
-      <x:c r="D7" s="46"/>
-      <x:c r="E7" s="46"/>
-      <x:c r="F7" s="46"/>
-      <x:c r="G7" s="46"/>
-      <x:c r="H7" s="46"/>
-      <x:c r="I7" s="46"/>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="40" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="B8" s="46"/>
-      <x:c r="C8" s="46"/>
-      <x:c r="D8" s="46"/>
-      <x:c r="E8" s="46"/>
-      <x:c r="F8" s="46"/>
-      <x:c r="G8" s="46"/>
-      <x:c r="H8" s="46"/>
-      <x:c r="I8" s="46"/>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
+      <x:c r="G8" s="40"/>
+      <x:c r="H8" s="40"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="40" t="str">
         <x:v>2026-11</x:v>
       </x:c>
-      <x:c r="B9" s="46"/>
-      <x:c r="C9" s="46"/>
-      <x:c r="D9" s="46"/>
-      <x:c r="E9" s="46"/>
-      <x:c r="F9" s="46"/>
-      <x:c r="G9" s="46"/>
-      <x:c r="H9" s="46"/>
-      <x:c r="I9" s="46"/>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="40" t="str">
         <x:v>2026-12</x:v>
       </x:c>
-      <x:c r="B10" s="46"/>
-      <x:c r="C10" s="46"/>
-      <x:c r="D10" s="46"/>
-      <x:c r="E10" s="46"/>
-      <x:c r="F10" s="46"/>
-      <x:c r="G10" s="46"/>
-      <x:c r="H10" s="46"/>
-      <x:c r="I10" s="46"/>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
+      <x:c r="G10" s="40"/>
+      <x:c r="H10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="40" t="str">
         <x:v>2027-01</x:v>
       </x:c>
-      <x:c r="B11" s="46"/>
-      <x:c r="C11" s="46"/>
-      <x:c r="D11" s="46"/>
-      <x:c r="E11" s="46"/>
-      <x:c r="F11" s="46"/>
-      <x:c r="G11" s="46"/>
-      <x:c r="H11" s="46"/>
-      <x:c r="I11" s="46"/>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="46" t="str">
+      <x:c r="A12" s="40" t="str">
         <x:v>2027-02</x:v>
       </x:c>
-      <x:c r="B12" s="46"/>
-      <x:c r="C12" s="46"/>
-      <x:c r="D12" s="46"/>
-      <x:c r="E12" s="46"/>
-      <x:c r="F12" s="46"/>
-      <x:c r="G12" s="46"/>
-      <x:c r="H12" s="46"/>
-      <x:c r="I12" s="46"/>
+      <x:c r="B12" s="40"/>
+      <x:c r="C12" s="40"/>
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="40"/>
+      <x:c r="F12" s="40"/>
+      <x:c r="G12" s="40"/>
+      <x:c r="H12" s="40"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="46" t="str">
+      <x:c r="A13" s="40" t="str">
         <x:v>2027-03</x:v>
       </x:c>
-      <x:c r="B13" s="46"/>
-      <x:c r="C13" s="46"/>
-      <x:c r="D13" s="46"/>
-      <x:c r="E13" s="46"/>
-      <x:c r="F13" s="46"/>
-      <x:c r="G13" s="46"/>
-      <x:c r="H13" s="46"/>
-      <x:c r="I13" s="46"/>
+      <x:c r="B13" s="40"/>
+      <x:c r="C13" s="40"/>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="46" t="str">
+      <x:c r="A14" s="40" t="str">
         <x:v>2027-04</x:v>
       </x:c>
-      <x:c r="B14" s="46"/>
-      <x:c r="C14" s="46"/>
-      <x:c r="D14" s="46"/>
-      <x:c r="E14" s="46"/>
-      <x:c r="F14" s="46"/>
-      <x:c r="G14" s="46"/>
-      <x:c r="H14" s="46"/>
-      <x:c r="I14" s="46"/>
+      <x:c r="B14" s="40"/>
+      <x:c r="C14" s="40"/>
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="40"/>
+      <x:c r="F14" s="40"/>
+      <x:c r="G14" s="40"/>
+      <x:c r="H14" s="40"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="46" t="str">
+      <x:c r="A15" s="40" t="str">
         <x:v>2027-05</x:v>
       </x:c>
-      <x:c r="B15" s="46"/>
-      <x:c r="C15" s="46"/>
-      <x:c r="D15" s="46"/>
-      <x:c r="E15" s="46"/>
-      <x:c r="F15" s="46"/>
-      <x:c r="G15" s="46"/>
-      <x:c r="H15" s="46"/>
-      <x:c r="I15" s="46"/>
+      <x:c r="B15" s="40"/>
+      <x:c r="C15" s="40"/>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="47" t="str">
+      <x:c r="A16" s="41" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="B16" s="47"/>
-      <x:c r="C16" s="47"/>
-      <x:c r="D16" s="47"/>
-      <x:c r="E16" s="47"/>
-      <x:c r="F16" s="47"/>
-      <x:c r="G16" s="47"/>
-      <x:c r="H16" s="47"/>
-      <x:c r="I16" s="47"/>
+      <x:c r="B16" s="41"/>
+      <x:c r="C16" s="41"/>
+      <x:c r="D16" s="41"/>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16" s="41"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7979,22 +8434,21 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>FY27 capacity response | case comparison</x:v>
+        <x:v>FY27 delivery analysis | working model</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -8005,11 +8459,10 @@
       <x:c r="H1" s="3"/>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Capacity gap = required hours less available hours; positive is a shortfall and negative is spare capacity</x:v>
+        <x:v>Show the operating conclusion and retain a check to the supporting schedules</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -8020,455 +8473,211 @@
       <x:c r="H2" s="6"/>
       <x:c r="I2" s="6"/>
       <x:c r="J2" s="6"/>
-      <x:c r="K2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Case</x:v>
+        <x:v>Period</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Month</x:v>
+        <x:v>Basis</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>Revenue</x:v>
+        <x:v>Requirement</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Required hours</x:v>
+        <x:v>Availability</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>Available hours</x:v>
+        <x:v>Variance</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>Capacity gap</x:v>
+        <x:v>Authorized response</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>Emergency OT used</x:v>
+        <x:v>Residual</x:v>
       </x:c>
       <x:c r="H4" s="16" t="str">
-        <x:v>Surge used</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="I4" s="16" t="str">
-        <x:v>Unresolved shortfall</x:v>
-      </x:c>
-      <x:c r="J4" s="16" t="str">
-        <x:v>Remediation cost</x:v>
-      </x:c>
-      <x:c r="K4" s="17" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="J4" s="17" t="str">
+        <x:v>Source / check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="45" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B5" s="45" t="str">
+      <x:c r="A5" s="39" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="C5" s="45"/>
-      <x:c r="D5" s="45"/>
-      <x:c r="E5" s="45"/>
-      <x:c r="F5" s="45"/>
-      <x:c r="G5" s="45"/>
-      <x:c r="H5" s="45"/>
-      <x:c r="I5" s="45"/>
-      <x:c r="J5" s="45"/>
-      <x:c r="K5" s="45"/>
+      <x:c r="B5" s="39"/>
+      <x:c r="C5" s="39"/>
+      <x:c r="D5" s="39"/>
+      <x:c r="E5" s="39"/>
+      <x:c r="F5" s="39"/>
+      <x:c r="G5" s="39"/>
+      <x:c r="H5" s="39"/>
+      <x:c r="I5" s="39"/>
+      <x:c r="J5" s="39"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="40" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="C6" s="46"/>
-      <x:c r="D6" s="46"/>
-      <x:c r="E6" s="46"/>
-      <x:c r="F6" s="46"/>
-      <x:c r="G6" s="46"/>
-      <x:c r="H6" s="46"/>
-      <x:c r="I6" s="46"/>
-      <x:c r="J6" s="46"/>
-      <x:c r="K6" s="46"/>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
+      <x:c r="G6" s="40"/>
+      <x:c r="H6" s="40"/>
+      <x:c r="I6" s="40"/>
+      <x:c r="J6" s="40"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="A7" s="40" t="str">
         <x:v>2026-09</x:v>
       </x:c>
-      <x:c r="C7" s="46"/>
-      <x:c r="D7" s="46"/>
-      <x:c r="E7" s="46"/>
-      <x:c r="F7" s="46"/>
-      <x:c r="G7" s="46"/>
-      <x:c r="H7" s="46"/>
-      <x:c r="I7" s="46"/>
-      <x:c r="J7" s="46"/>
-      <x:c r="K7" s="46"/>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="40"/>
+      <x:c r="J7" s="40"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="A8" s="40" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="C8" s="46"/>
-      <x:c r="D8" s="46"/>
-      <x:c r="E8" s="46"/>
-      <x:c r="F8" s="46"/>
-      <x:c r="G8" s="46"/>
-      <x:c r="H8" s="46"/>
-      <x:c r="I8" s="46"/>
-      <x:c r="J8" s="46"/>
-      <x:c r="K8" s="46"/>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
+      <x:c r="G8" s="40"/>
+      <x:c r="H8" s="40"/>
+      <x:c r="I8" s="40"/>
+      <x:c r="J8" s="40"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="A9" s="40" t="str">
         <x:v>2026-11</x:v>
       </x:c>
-      <x:c r="C9" s="46"/>
-      <x:c r="D9" s="46"/>
-      <x:c r="E9" s="46"/>
-      <x:c r="F9" s="46"/>
-      <x:c r="G9" s="46"/>
-      <x:c r="H9" s="46"/>
-      <x:c r="I9" s="46"/>
-      <x:c r="J9" s="46"/>
-      <x:c r="K9" s="46"/>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="40"/>
+      <x:c r="J9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="A10" s="40" t="str">
         <x:v>2026-12</x:v>
       </x:c>
-      <x:c r="C10" s="46"/>
-      <x:c r="D10" s="46"/>
-      <x:c r="E10" s="46"/>
-      <x:c r="F10" s="46"/>
-      <x:c r="G10" s="46"/>
-      <x:c r="H10" s="46"/>
-      <x:c r="I10" s="46"/>
-      <x:c r="J10" s="46"/>
-      <x:c r="K10" s="46"/>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
+      <x:c r="G10" s="40"/>
+      <x:c r="H10" s="40"/>
+      <x:c r="I10" s="40"/>
+      <x:c r="J10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="A11" s="40" t="str">
         <x:v>2027-01</x:v>
       </x:c>
-      <x:c r="C11" s="46"/>
-      <x:c r="D11" s="46"/>
-      <x:c r="E11" s="46"/>
-      <x:c r="F11" s="46"/>
-      <x:c r="G11" s="46"/>
-      <x:c r="H11" s="46"/>
-      <x:c r="I11" s="46"/>
-      <x:c r="J11" s="46"/>
-      <x:c r="K11" s="46"/>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40"/>
+      <x:c r="I11" s="40"/>
+      <x:c r="J11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="A12" s="40" t="str">
         <x:v>2027-02</x:v>
       </x:c>
-      <x:c r="C12" s="46"/>
-      <x:c r="D12" s="46"/>
-      <x:c r="E12" s="46"/>
-      <x:c r="F12" s="46"/>
-      <x:c r="G12" s="46"/>
-      <x:c r="H12" s="46"/>
-      <x:c r="I12" s="46"/>
-      <x:c r="J12" s="46"/>
-      <x:c r="K12" s="46"/>
+      <x:c r="B12" s="40"/>
+      <x:c r="C12" s="40"/>
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="40"/>
+      <x:c r="F12" s="40"/>
+      <x:c r="G12" s="40"/>
+      <x:c r="H12" s="40"/>
+      <x:c r="I12" s="40"/>
+      <x:c r="J12" s="40"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="A13" s="40" t="str">
         <x:v>2027-03</x:v>
       </x:c>
-      <x:c r="C13" s="46"/>
-      <x:c r="D13" s="46"/>
-      <x:c r="E13" s="46"/>
-      <x:c r="F13" s="46"/>
-      <x:c r="G13" s="46"/>
-      <x:c r="H13" s="46"/>
-      <x:c r="I13" s="46"/>
-      <x:c r="J13" s="46"/>
-      <x:c r="K13" s="46"/>
+      <x:c r="B13" s="40"/>
+      <x:c r="C13" s="40"/>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40"/>
+      <x:c r="I13" s="40"/>
+      <x:c r="J13" s="40"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="A14" s="40" t="str">
         <x:v>2027-04</x:v>
       </x:c>
-      <x:c r="C14" s="46"/>
-      <x:c r="D14" s="46"/>
-      <x:c r="E14" s="46"/>
-      <x:c r="F14" s="46"/>
-      <x:c r="G14" s="46"/>
-      <x:c r="H14" s="46"/>
-      <x:c r="I14" s="46"/>
-      <x:c r="J14" s="46"/>
-      <x:c r="K14" s="46"/>
+      <x:c r="B14" s="40"/>
+      <x:c r="C14" s="40"/>
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="40"/>
+      <x:c r="F14" s="40"/>
+      <x:c r="G14" s="40"/>
+      <x:c r="H14" s="40"/>
+      <x:c r="I14" s="40"/>
+      <x:c r="J14" s="40"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="A15" s="40" t="str">
         <x:v>2027-05</x:v>
       </x:c>
-      <x:c r="C15" s="46"/>
-      <x:c r="D15" s="46"/>
-      <x:c r="E15" s="46"/>
-      <x:c r="F15" s="46"/>
-      <x:c r="G15" s="46"/>
-      <x:c r="H15" s="46"/>
-      <x:c r="I15" s="46"/>
-      <x:c r="J15" s="46"/>
-      <x:c r="K15" s="46"/>
+      <x:c r="B15" s="40"/>
+      <x:c r="C15" s="40"/>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40"/>
+      <x:c r="I15" s="40"/>
+      <x:c r="J15" s="40"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="46" t="str">
-        <x:v>Approved probability plan</x:v>
-      </x:c>
-      <x:c r="B16" s="46" t="str">
+      <x:c r="A16" s="41" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="C16" s="46"/>
-      <x:c r="D16" s="46"/>
-      <x:c r="E16" s="46"/>
-      <x:c r="F16" s="46"/>
-      <x:c r="G16" s="46"/>
-      <x:c r="H16" s="46"/>
-      <x:c r="I16" s="46"/>
-      <x:c r="J16" s="46"/>
-      <x:c r="K16" s="46"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B17" s="46" t="str">
-        <x:v>2026-07</x:v>
-      </x:c>
-      <x:c r="C17" s="46"/>
-      <x:c r="D17" s="46"/>
-      <x:c r="E17" s="46"/>
-      <x:c r="F17" s="46"/>
-      <x:c r="G17" s="46"/>
-      <x:c r="H17" s="46"/>
-      <x:c r="I17" s="46"/>
-      <x:c r="J17" s="46"/>
-      <x:c r="K17" s="46"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="str">
-        <x:v>2026-08</x:v>
-      </x:c>
-      <x:c r="C18" s="46"/>
-      <x:c r="D18" s="46"/>
-      <x:c r="E18" s="46"/>
-      <x:c r="F18" s="46"/>
-      <x:c r="G18" s="46"/>
-      <x:c r="H18" s="46"/>
-      <x:c r="I18" s="46"/>
-      <x:c r="J18" s="46"/>
-      <x:c r="K18" s="46"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
-        <x:v>2026-09</x:v>
-      </x:c>
-      <x:c r="C19" s="46"/>
-      <x:c r="D19" s="46"/>
-      <x:c r="E19" s="46"/>
-      <x:c r="F19" s="46"/>
-      <x:c r="G19" s="46"/>
-      <x:c r="H19" s="46"/>
-      <x:c r="I19" s="46"/>
-      <x:c r="J19" s="46"/>
-      <x:c r="K19" s="46"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B20" s="46" t="str">
-        <x:v>2026-10</x:v>
-      </x:c>
-      <x:c r="C20" s="46"/>
-      <x:c r="D20" s="46"/>
-      <x:c r="E20" s="46"/>
-      <x:c r="F20" s="46"/>
-      <x:c r="G20" s="46"/>
-      <x:c r="H20" s="46"/>
-      <x:c r="I20" s="46"/>
-      <x:c r="J20" s="46"/>
-      <x:c r="K20" s="46"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B21" s="46" t="str">
-        <x:v>2026-11</x:v>
-      </x:c>
-      <x:c r="C21" s="46"/>
-      <x:c r="D21" s="46"/>
-      <x:c r="E21" s="46"/>
-      <x:c r="F21" s="46"/>
-      <x:c r="G21" s="46"/>
-      <x:c r="H21" s="46"/>
-      <x:c r="I21" s="46"/>
-      <x:c r="J21" s="46"/>
-      <x:c r="K21" s="46"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B22" s="46" t="str">
-        <x:v>2026-12</x:v>
-      </x:c>
-      <x:c r="C22" s="46"/>
-      <x:c r="D22" s="46"/>
-      <x:c r="E22" s="46"/>
-      <x:c r="F22" s="46"/>
-      <x:c r="G22" s="46"/>
-      <x:c r="H22" s="46"/>
-      <x:c r="I22" s="46"/>
-      <x:c r="J22" s="46"/>
-      <x:c r="K22" s="46"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B23" s="46" t="str">
-        <x:v>2027-01</x:v>
-      </x:c>
-      <x:c r="C23" s="46"/>
-      <x:c r="D23" s="46"/>
-      <x:c r="E23" s="46"/>
-      <x:c r="F23" s="46"/>
-      <x:c r="G23" s="46"/>
-      <x:c r="H23" s="46"/>
-      <x:c r="I23" s="46"/>
-      <x:c r="J23" s="46"/>
-      <x:c r="K23" s="46"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B24" s="46" t="str">
-        <x:v>2027-02</x:v>
-      </x:c>
-      <x:c r="C24" s="46"/>
-      <x:c r="D24" s="46"/>
-      <x:c r="E24" s="46"/>
-      <x:c r="F24" s="46"/>
-      <x:c r="G24" s="46"/>
-      <x:c r="H24" s="46"/>
-      <x:c r="I24" s="46"/>
-      <x:c r="J24" s="46"/>
-      <x:c r="K24" s="46"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B25" s="46" t="str">
-        <x:v>2027-03</x:v>
-      </x:c>
-      <x:c r="C25" s="46"/>
-      <x:c r="D25" s="46"/>
-      <x:c r="E25" s="46"/>
-      <x:c r="F25" s="46"/>
-      <x:c r="G25" s="46"/>
-      <x:c r="H25" s="46"/>
-      <x:c r="I25" s="46"/>
-      <x:c r="J25" s="46"/>
-      <x:c r="K25" s="46"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B26" s="46" t="str">
-        <x:v>2027-04</x:v>
-      </x:c>
-      <x:c r="C26" s="46"/>
-      <x:c r="D26" s="46"/>
-      <x:c r="E26" s="46"/>
-      <x:c r="F26" s="46"/>
-      <x:c r="G26" s="46"/>
-      <x:c r="H26" s="46"/>
-      <x:c r="I26" s="46"/>
-      <x:c r="J26" s="46"/>
-      <x:c r="K26" s="46"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="46" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B27" s="46" t="str">
-        <x:v>2027-05</x:v>
-      </x:c>
-      <x:c r="C27" s="46"/>
-      <x:c r="D27" s="46"/>
-      <x:c r="E27" s="46"/>
-      <x:c r="F27" s="46"/>
-      <x:c r="G27" s="46"/>
-      <x:c r="H27" s="46"/>
-      <x:c r="I27" s="46"/>
-      <x:c r="J27" s="46"/>
-      <x:c r="K27" s="46"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="47" t="str">
-        <x:v>Full signed commitment</x:v>
-      </x:c>
-      <x:c r="B28" s="47" t="str">
-        <x:v>2027-06</x:v>
-      </x:c>
-      <x:c r="C28" s="47"/>
-      <x:c r="D28" s="47"/>
-      <x:c r="E28" s="47"/>
-      <x:c r="F28" s="47"/>
-      <x:c r="G28" s="47"/>
-      <x:c r="H28" s="47"/>
-      <x:c r="I28" s="47"/>
-      <x:c r="J28" s="47"/>
-      <x:c r="K28" s="47"/>
+      <x:c r="B16" s="41"/>
+      <x:c r="C16" s="41"/>
+      <x:c r="D16" s="41"/>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16" s="41"/>
+      <x:c r="I16" s="41"/>
+      <x:c r="J16" s="41"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K2"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8479,21 +8688,20 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>FY27 signed-backlog execution | priority and earnings</x:v>
+        <x:v>FY27 project delivery | working model</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -8504,11 +8712,10 @@
       <x:c r="H1" s="3"/>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Use approved customer priority and contract terms; roll unfinished work rather than manufacturing capacity</x:v>
+        <x:v>Complete the project-level view and retain the calculation trail</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -8519,323 +8726,155 @@
       <x:c r="H2" s="6"/>
       <x:c r="I2" s="6"/>
       <x:c r="J2" s="6"/>
-      <x:c r="K2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
         <x:v>Project</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Priority</x:v>
+        <x:v>Priority / sequence</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>Signed backlog</x:v>
+        <x:v>Scheduled work</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Required hours</x:v>
+        <x:v>Delivered work</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>Completed hours</x:v>
+        <x:v>Carryforward</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>Deferred hours</x:v>
+        <x:v>Revenue effect</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>Completed revenue</x:v>
+        <x:v>Margin effect</x:v>
       </x:c>
       <x:c r="H4" s="16" t="str">
-        <x:v>Deferred revenue</x:v>
+        <x:v>Contract effect</x:v>
       </x:c>
       <x:c r="I4" s="16" t="str">
-        <x:v>Completed gross profit</x:v>
-      </x:c>
-      <x:c r="J4" s="16" t="str">
-        <x:v>Liquidated damages</x:v>
-      </x:c>
-      <x:c r="K4" s="17" t="str">
-        <x:v>Release decision</x:v>
+        <x:v>Disposition</x:v>
+      </x:c>
+      <x:c r="J4" s="17" t="str">
+        <x:v>Source / check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="45" t="str">
+      <x:c r="A5" s="39" t="str">
         <x:v>P-3101</x:v>
       </x:c>
-      <x:c r="B5" s="45"/>
-      <x:c r="C5" s="45"/>
-      <x:c r="D5" s="45"/>
-      <x:c r="E5" s="45"/>
-      <x:c r="F5" s="45"/>
-      <x:c r="G5" s="45"/>
-      <x:c r="H5" s="45"/>
-      <x:c r="I5" s="45"/>
-      <x:c r="J5" s="45"/>
-      <x:c r="K5" s="45"/>
+      <x:c r="B5" s="39"/>
+      <x:c r="C5" s="39"/>
+      <x:c r="D5" s="39"/>
+      <x:c r="E5" s="39"/>
+      <x:c r="F5" s="39"/>
+      <x:c r="G5" s="39"/>
+      <x:c r="H5" s="39"/>
+      <x:c r="I5" s="39"/>
+      <x:c r="J5" s="39"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="46" t="str">
+      <x:c r="A6" s="40" t="str">
         <x:v>P-3107</x:v>
       </x:c>
-      <x:c r="B6" s="46"/>
-      <x:c r="C6" s="46"/>
-      <x:c r="D6" s="46"/>
-      <x:c r="E6" s="46"/>
-      <x:c r="F6" s="46"/>
-      <x:c r="G6" s="46"/>
-      <x:c r="H6" s="46"/>
-      <x:c r="I6" s="46"/>
-      <x:c r="J6" s="46"/>
-      <x:c r="K6" s="46"/>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
+      <x:c r="G6" s="40"/>
+      <x:c r="H6" s="40"/>
+      <x:c r="I6" s="40"/>
+      <x:c r="J6" s="40"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="A7" s="40" t="str">
         <x:v>P-3114</x:v>
       </x:c>
-      <x:c r="B7" s="46"/>
-      <x:c r="C7" s="46"/>
-      <x:c r="D7" s="46"/>
-      <x:c r="E7" s="46"/>
-      <x:c r="F7" s="46"/>
-      <x:c r="G7" s="46"/>
-      <x:c r="H7" s="46"/>
-      <x:c r="I7" s="46"/>
-      <x:c r="J7" s="46"/>
-      <x:c r="K7" s="46"/>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="40"/>
+      <x:c r="J7" s="40"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="46" t="str">
+      <x:c r="A8" s="40" t="str">
         <x:v>P-3122</x:v>
       </x:c>
-      <x:c r="B8" s="46"/>
-      <x:c r="C8" s="46"/>
-      <x:c r="D8" s="46"/>
-      <x:c r="E8" s="46"/>
-      <x:c r="F8" s="46"/>
-      <x:c r="G8" s="46"/>
-      <x:c r="H8" s="46"/>
-      <x:c r="I8" s="46"/>
-      <x:c r="J8" s="46"/>
-      <x:c r="K8" s="46"/>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
+      <x:c r="G8" s="40"/>
+      <x:c r="H8" s="40"/>
+      <x:c r="I8" s="40"/>
+      <x:c r="J8" s="40"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="46" t="str">
+      <x:c r="A9" s="40" t="str">
         <x:v>P-3130</x:v>
       </x:c>
-      <x:c r="B9" s="46"/>
-      <x:c r="C9" s="46"/>
-      <x:c r="D9" s="46"/>
-      <x:c r="E9" s="46"/>
-      <x:c r="F9" s="46"/>
-      <x:c r="G9" s="46"/>
-      <x:c r="H9" s="46"/>
-      <x:c r="I9" s="46"/>
-      <x:c r="J9" s="46"/>
-      <x:c r="K9" s="46"/>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="40"/>
+      <x:c r="J9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="46" t="str">
+      <x:c r="A10" s="40" t="str">
         <x:v>P-3138</x:v>
       </x:c>
-      <x:c r="B10" s="46"/>
-      <x:c r="C10" s="46"/>
-      <x:c r="D10" s="46"/>
-      <x:c r="E10" s="46"/>
-      <x:c r="F10" s="46"/>
-      <x:c r="G10" s="46"/>
-      <x:c r="H10" s="46"/>
-      <x:c r="I10" s="46"/>
-      <x:c r="J10" s="46"/>
-      <x:c r="K10" s="46"/>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
+      <x:c r="G10" s="40"/>
+      <x:c r="H10" s="40"/>
+      <x:c r="I10" s="40"/>
+      <x:c r="J10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="46" t="str">
+      <x:c r="A11" s="40" t="str">
         <x:v>P-3145</x:v>
       </x:c>
-      <x:c r="B11" s="46"/>
-      <x:c r="C11" s="46"/>
-      <x:c r="D11" s="46"/>
-      <x:c r="E11" s="46"/>
-      <x:c r="F11" s="46"/>
-      <x:c r="G11" s="46"/>
-      <x:c r="H11" s="46"/>
-      <x:c r="I11" s="46"/>
-      <x:c r="J11" s="46"/>
-      <x:c r="K11" s="46"/>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40"/>
+      <x:c r="I11" s="40"/>
+      <x:c r="J11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="47" t="str">
+      <x:c r="A12" s="41" t="str">
         <x:v>P-3152</x:v>
       </x:c>
-      <x:c r="B12" s="47"/>
-      <x:c r="C12" s="47"/>
-      <x:c r="D12" s="47"/>
-      <x:c r="E12" s="47"/>
-      <x:c r="F12" s="47"/>
-      <x:c r="G12" s="47"/>
-      <x:c r="H12" s="47"/>
-      <x:c r="I12" s="47"/>
-      <x:c r="J12" s="47"/>
-      <x:c r="K12" s="47"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="48" t="str">
-        <x:v>MONTHLY EARNINGS RELEASE BRIDGE</x:v>
-      </x:c>
-      <x:c r="B15" s="48"/>
-      <x:c r="C15" s="48"/>
-      <x:c r="D15" s="48"/>
-      <x:c r="E15" s="48"/>
-      <x:c r="F15" s="48"/>
-      <x:c r="G15" s="48"/>
-      <x:c r="H15" s="48"/>
-      <x:c r="I15" s="48"/>
-      <x:c r="J15" s="48"/>
-      <x:c r="K15" s="48"/>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="15" t="str">
-        <x:v>Month</x:v>
-      </x:c>
-      <x:c r="B16" s="16" t="str">
-        <x:v>Probability-plan GP after response</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="str">
-        <x:v>Gross-commitment GP after response</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="str">
-        <x:v>Executable GP after damages</x:v>
-      </x:c>
-      <x:c r="E16" s="16" t="str">
-        <x:v>Deferred revenue at risk</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="str">
-        <x:v>Management decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="45" t="str">
-        <x:v>2026-07</x:v>
-      </x:c>
-      <x:c r="B17" s="45"/>
-      <x:c r="C17" s="45"/>
-      <x:c r="D17" s="45"/>
-      <x:c r="E17" s="45"/>
-      <x:c r="F17" s="45"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="46" t="str">
-        <x:v>2026-08</x:v>
-      </x:c>
-      <x:c r="B18" s="46"/>
-      <x:c r="C18" s="46"/>
-      <x:c r="D18" s="46"/>
-      <x:c r="E18" s="46"/>
-      <x:c r="F18" s="46"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="46" t="str">
-        <x:v>2026-09</x:v>
-      </x:c>
-      <x:c r="B19" s="46"/>
-      <x:c r="C19" s="46"/>
-      <x:c r="D19" s="46"/>
-      <x:c r="E19" s="46"/>
-      <x:c r="F19" s="46"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="46" t="str">
-        <x:v>2026-10</x:v>
-      </x:c>
-      <x:c r="B20" s="46"/>
-      <x:c r="C20" s="46"/>
-      <x:c r="D20" s="46"/>
-      <x:c r="E20" s="46"/>
-      <x:c r="F20" s="46"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="46" t="str">
-        <x:v>2026-11</x:v>
-      </x:c>
-      <x:c r="B21" s="46"/>
-      <x:c r="C21" s="46"/>
-      <x:c r="D21" s="46"/>
-      <x:c r="E21" s="46"/>
-      <x:c r="F21" s="46"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="46" t="str">
-        <x:v>2026-12</x:v>
-      </x:c>
-      <x:c r="B22" s="46"/>
-      <x:c r="C22" s="46"/>
-      <x:c r="D22" s="46"/>
-      <x:c r="E22" s="46"/>
-      <x:c r="F22" s="46"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="46" t="str">
-        <x:v>2027-01</x:v>
-      </x:c>
-      <x:c r="B23" s="46"/>
-      <x:c r="C23" s="46"/>
-      <x:c r="D23" s="46"/>
-      <x:c r="E23" s="46"/>
-      <x:c r="F23" s="46"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="46" t="str">
-        <x:v>2027-02</x:v>
-      </x:c>
-      <x:c r="B24" s="46"/>
-      <x:c r="C24" s="46"/>
-      <x:c r="D24" s="46"/>
-      <x:c r="E24" s="46"/>
-      <x:c r="F24" s="46"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="46" t="str">
-        <x:v>2027-03</x:v>
-      </x:c>
-      <x:c r="B25" s="46"/>
-      <x:c r="C25" s="46"/>
-      <x:c r="D25" s="46"/>
-      <x:c r="E25" s="46"/>
-      <x:c r="F25" s="46"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="46" t="str">
-        <x:v>2027-04</x:v>
-      </x:c>
-      <x:c r="B26" s="46"/>
-      <x:c r="C26" s="46"/>
-      <x:c r="D26" s="46"/>
-      <x:c r="E26" s="46"/>
-      <x:c r="F26" s="46"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="46" t="str">
-        <x:v>2027-05</x:v>
-      </x:c>
-      <x:c r="B27" s="46"/>
-      <x:c r="C27" s="46"/>
-      <x:c r="D27" s="46"/>
-      <x:c r="E27" s="46"/>
-      <x:c r="F27" s="46"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="47" t="str">
-        <x:v>2027-06</x:v>
-      </x:c>
-      <x:c r="B28" s="47"/>
-      <x:c r="C28" s="47"/>
-      <x:c r="D28" s="47"/>
-      <x:c r="E28" s="47"/>
-      <x:c r="F28" s="47"/>
+      <x:c r="B12" s="41"/>
+      <x:c r="C12" s="41"/>
+      <x:c r="D12" s="41"/>
+      <x:c r="E12" s="41"/>
+      <x:c r="F12" s="41"/>
+      <x:c r="G12" s="41"/>
+      <x:c r="H12" s="41"/>
+      <x:c r="I12" s="41"/>
+      <x:c r="J12" s="41"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K2"/>
-    <x:mergeCell ref="A15:K15"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8846,230 +8885,168 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>FY27 backlog and capacity | controls and executive decision</x:v>
+        <x:v>FY27 backlog delivery | review and controls</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
       <x:c r="D1" s="3"/>
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>One assertion per control; the model is releasable only when the calculations and decision conditions agree</x:v>
+        <x:v>Complete the control rows and management summary before review</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
       <x:c r="D2" s="6"/>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
-      <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-      <x:c r="I2" s="6"/>
-      <x:c r="J2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Check</x:v>
+        <x:v>Control</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Result</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>Expected</x:v>
+        <x:v>Expectation</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Difference</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>Tolerance</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="str">
-        <x:v>Where to fix / source</x:v>
+      <x:c r="F4" s="17" t="str">
+        <x:v>Source / resolution</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="35" t="str">
-        <x:v>Source population tie</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
-      <x:c r="C5" s="35"/>
-      <x:c r="D5" s="35"/>
-      <x:c r="E5" s="35"/>
-      <x:c r="F5" s="35"/>
-      <x:c r="G5" s="35"/>
+      <x:c r="A5" s="39"/>
+      <x:c r="B5" s="39"/>
+      <x:c r="C5" s="39"/>
+      <x:c r="D5" s="39"/>
+      <x:c r="E5" s="39"/>
+      <x:c r="F5" s="39"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="50" t="str">
-        <x:v>Backlog roll-forward</x:v>
-      </x:c>
-      <x:c r="B6" s="50"/>
-      <x:c r="C6" s="50"/>
-      <x:c r="D6" s="50"/>
-      <x:c r="E6" s="50"/>
-      <x:c r="F6" s="50"/>
-      <x:c r="G6" s="50"/>
+      <x:c r="A6" s="40"/>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="50" t="str">
-        <x:v>Probability-plan burn</x:v>
-      </x:c>
-      <x:c r="B7" s="50"/>
-      <x:c r="C7" s="50"/>
-      <x:c r="D7" s="50"/>
-      <x:c r="E7" s="50"/>
-      <x:c r="F7" s="50"/>
-      <x:c r="G7" s="50"/>
+      <x:c r="A7" s="40"/>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="50" t="str">
-        <x:v>Gross-commitment burn</x:v>
-      </x:c>
-      <x:c r="B8" s="50"/>
-      <x:c r="C8" s="50"/>
-      <x:c r="D8" s="50"/>
-      <x:c r="E8" s="50"/>
-      <x:c r="F8" s="50"/>
-      <x:c r="G8" s="50"/>
+      <x:c r="A8" s="40"/>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="50" t="str">
-        <x:v>Capacity sign convention</x:v>
-      </x:c>
-      <x:c r="B9" s="50"/>
-      <x:c r="C9" s="50"/>
-      <x:c r="D9" s="50"/>
-      <x:c r="E9" s="50"/>
-      <x:c r="F9" s="50"/>
-      <x:c r="G9" s="50"/>
+      <x:c r="A9" s="40"/>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="50" t="str">
-        <x:v>Remediation sequence</x:v>
-      </x:c>
-      <x:c r="B10" s="50"/>
-      <x:c r="C10" s="50"/>
-      <x:c r="D10" s="50"/>
-      <x:c r="E10" s="50"/>
-      <x:c r="F10" s="50"/>
-      <x:c r="G10" s="50"/>
+      <x:c r="A10" s="40"/>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="50" t="str">
-        <x:v>Project-to-month roll-forward</x:v>
-      </x:c>
-      <x:c r="B11" s="50"/>
-      <x:c r="C11" s="50"/>
-      <x:c r="D11" s="50"/>
-      <x:c r="E11" s="50"/>
-      <x:c r="F11" s="50"/>
-      <x:c r="G11" s="50"/>
+      <x:c r="A11" s="40"/>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="50" t="str">
-        <x:v>Revenue and gross-profit bridge</x:v>
-      </x:c>
-      <x:c r="B12" s="50"/>
-      <x:c r="C12" s="50"/>
-      <x:c r="D12" s="50"/>
-      <x:c r="E12" s="50"/>
-      <x:c r="F12" s="50"/>
-      <x:c r="G12" s="50"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="36" t="str">
-        <x:v>MODEL STATUS</x:v>
-      </x:c>
-      <x:c r="B13" s="36"/>
-      <x:c r="C13" s="36"/>
-      <x:c r="D13" s="36"/>
-      <x:c r="E13" s="36"/>
-      <x:c r="F13" s="36"/>
-      <x:c r="G13" s="36"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="48" t="str">
-        <x:v>EXECUTIVE RECOVERY DECISION</x:v>
-      </x:c>
-      <x:c r="B16" s="48"/>
-      <x:c r="C16" s="48"/>
-      <x:c r="D16" s="48"/>
-      <x:c r="E16" s="48"/>
-      <x:c r="F16" s="48"/>
-      <x:c r="G16" s="48"/>
-      <x:c r="H16" s="48"/>
-      <x:c r="I16" s="48"/>
-      <x:c r="J16" s="48"/>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="15" t="str">
+      <x:c r="A12" s="41"/>
+      <x:c r="B12" s="41"/>
+      <x:c r="C12" s="41"/>
+      <x:c r="D12" s="41"/>
+      <x:c r="E12" s="41"/>
+      <x:c r="F12" s="41"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="42" t="str">
+        <x:v>MANAGEMENT SUMMARY</x:v>
+      </x:c>
+      <x:c r="B15" s="42"/>
+      <x:c r="C15" s="42"/>
+      <x:c r="D15" s="42"/>
+      <x:c r="E15" s="42"/>
+      <x:c r="F15" s="42"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="15" t="str">
         <x:v>Recommendation</x:v>
       </x:c>
-      <x:c r="B17" s="16" t="str">
-        <x:v>Probability-plan GP</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="str">
-        <x:v>Gross-commitment GP</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="str">
-        <x:v>Executable GP after damages</x:v>
-      </x:c>
-      <x:c r="E17" s="16" t="str">
-        <x:v>Deferred revenue</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="str">
-        <x:v>Deferred gross profit</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="str">
-        <x:v>Damages</x:v>
-      </x:c>
-      <x:c r="H17" s="16" t="str">
-        <x:v>Recovery required</x:v>
-      </x:c>
-      <x:c r="I17" s="16" t="str">
-        <x:v>Priority item</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="str">
-        <x:v>Release condition / owner action</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="51"/>
-      <x:c r="B18" s="51"/>
-      <x:c r="C18" s="51"/>
-      <x:c r="D18" s="51"/>
-      <x:c r="E18" s="51"/>
-      <x:c r="F18" s="51"/>
-      <x:c r="G18" s="51"/>
-      <x:c r="H18" s="51"/>
-      <x:c r="I18" s="51"/>
-      <x:c r="J18" s="51"/>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Delivery outlook</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>Financial exposure</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>Contract considerations</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>Required action</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>Decision owner / date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="47"/>
+      <x:c r="B17" s="47"/>
+      <x:c r="C17" s="47"/>
+      <x:c r="D17" s="47"/>
+      <x:c r="E17" s="47"/>
+      <x:c r="F17" s="47"/>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="48"/>
+      <x:c r="B18" s="48"/>
+      <x:c r="C18" s="48"/>
+      <x:c r="D18" s="48"/>
+      <x:c r="E18" s="48"/>
+      <x:c r="F18" s="48"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:J1"/>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="A16:J16"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A15:F15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
